--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O27" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="O29" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P29" t="n">
-        <v>3.68</v>
+        <v>2.57</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>5.31</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>8.65</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,13 +6926,13 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6965,10 +6965,10 @@
         <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.88194444445</v>
       </c>
     </row>
     <row r="42">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7188,7 +7188,7 @@
         <v>0</v>
       </c>
       <c r="AU42" s="3" t="n">
-        <v>46220.98958333334</v>
+        <v>46220.97569444445</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P27" t="n">
-        <v>3.68</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="O26" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="P26" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O26" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P26" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O27" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O28" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P28" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P27" t="n">
-        <v>3.68</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>3.68</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,7 +2629,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>3.68</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.89</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>3.45</v>
+        <v>3.38</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>3.68</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,13 +5813,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -5852,10 +5852,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1724,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1883,10 +1883,10 @@
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="O26" t="n">
-        <v>3.22</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.57</v>
+        <v>3.95</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,10 +4574,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="O27" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P27" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4739,10 +4739,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4898,10 +4898,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1847,40 +1847,40 @@
         <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>6.57</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC9" t="n">
         <v>1.95</v>
@@ -1889,13 +1889,13 @@
         <v>1.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>3.22</v>
       </c>
       <c r="P26" t="n">
-        <v>3.95</v>
+        <v>2.57</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4574,10 +4574,10 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="O28" t="n">
-        <v>3.38</v>
+        <v>2.4</v>
       </c>
       <c r="P28" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4892,16 +4892,16 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4064,13 +4064,13 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,13 +4382,13 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O26" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P26" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,13 +4700,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4733,10 +4733,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -4892,10 +4892,10 @@
         <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5057,10 +5057,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -5177,13 +5177,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>4.81</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -5534,10 +5534,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,23 +2470,23 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,13 +2495,13 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2513,25 +2513,25 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,17 +2629,17 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.05</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.15</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.38</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4421,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O26" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P26" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="O27" t="n">
-        <v>2.4</v>
+        <v>3.38</v>
       </c>
       <c r="P27" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="O29" t="n">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>3.67</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5186,28 +5186,28 @@
         <v>4.81</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y30" t="n">
         <v>1.58</v>
@@ -5216,25 +5216,25 @@
         <v>2.2</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>6.41</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,65 +5813,65 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.17</v>
+        <v>2.41</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>2.66</v>
       </c>
       <c r="P34" t="n">
-        <v>13</v>
+        <v>3.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.5</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="S34" t="n">
-        <v>1.13</v>
+        <v>1.67</v>
       </c>
       <c r="T34" t="n">
-        <v>5.5</v>
+        <v>2.15</v>
       </c>
       <c r="U34" t="n">
-        <v>1.62</v>
+        <v>4.05</v>
       </c>
       <c r="V34" t="n">
-        <v>2.15</v>
+        <v>1.16</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.05</v>
+        <v>1.63</v>
       </c>
       <c r="Z34" t="n">
-        <v>9</v>
+        <v>2.14</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.21</v>
+        <v>2.88</v>
       </c>
       <c r="AB34" t="n">
-        <v>4</v>
+        <v>1.32</v>
       </c>
       <c r="AC34" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG34" t="n">
         <v>1.53</v>
       </c>
-      <c r="AD34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AK34" t="n">
-        <v>3.65</v>
+        <v>1.44</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6935,34 +6935,34 @@
         <v>8.65</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="AA41" t="n">
         <v>1.57</v>
@@ -6971,19 +6971,19 @@
         <v>2.25</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7094,34 +7094,34 @@
         <v>2.54</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA42" t="n">
         <v>1.55</v>
@@ -7130,19 +7130,19 @@
         <v>2.3</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="O15" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P15" t="n">
-        <v>4.41</v>
+        <v>4.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="R15" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.34</v>
       </c>
-      <c r="S15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.37</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.75</v>
+        <v>4.38</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK15" t="n">
         <v>2</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P16" t="n">
-        <v>4.02</v>
+        <v>4.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="R16" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U16" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W16" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.38</v>
+        <v>3.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK16" t="n">
         <v>2</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4060,68 +4060,68 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.15</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.38</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,84 +4219,84 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.05</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF24" t="n">
+      <c r="AG24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK24" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="O26" t="n">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.4</v>
+        <v>3.36</v>
       </c>
       <c r="R26" t="n">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="S26" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="U26" t="n">
-        <v>2.88</v>
+        <v>4.4</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="W26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AD26" t="n">
         <v>1.05</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AE26" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>2.54</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.89</v>
+        <v>1.47</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="P31" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,65 +5813,65 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.41</v>
+        <v>1.17</v>
       </c>
       <c r="O34" t="n">
-        <v>2.66</v>
+        <v>6</v>
       </c>
       <c r="P34" t="n">
-        <v>3.23</v>
+        <v>13</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="R34" t="n">
-        <v>1.83</v>
+        <v>3.3</v>
       </c>
       <c r="S34" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="T34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V34" t="n">
         <v>2.15</v>
       </c>
-      <c r="U34" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.16</v>
-      </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="X34" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.63</v>
+        <v>1.05</v>
       </c>
       <c r="Z34" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2.14</v>
       </c>
-      <c r="AA34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.36</v>
+        <v>1.04</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.44</v>
+        <v>3.65</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,80 +6131,80 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.87</v>
+        <v>2.41</v>
       </c>
       <c r="O36" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="Q36" t="n">
         <v>3.1</v>
       </c>
-      <c r="P36" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2.66</v>
-      </c>
       <c r="R36" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="S36" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="T36" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="U36" t="n">
-        <v>2.63</v>
+        <v>4.05</v>
       </c>
       <c r="V36" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE36" t="n">
         <v>1.02</v>
       </c>
-      <c r="Y36" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD36" t="n">
+      <c r="AF36" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK36" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X37" t="n">
         <v>1.17</v>
       </c>
-      <c r="O37" t="n">
-        <v>6</v>
-      </c>
-      <c r="P37" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R37" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T37" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1</v>
-      </c>
       <c r="Y37" t="n">
-        <v>1.05</v>
+        <v>1.78</v>
       </c>
       <c r="Z37" t="n">
-        <v>9</v>
+        <v>2.02</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.21</v>
+        <v>3.2</v>
       </c>
       <c r="AB37" t="n">
-        <v>4</v>
+        <v>1.26</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.53</v>
+        <v>6.9</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.25</v>
+        <v>1.04</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="AK37" t="n">
-        <v>3.65</v>
+        <v>1.38</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC38" t="n">
         <v>2.6</v>
       </c>
-      <c r="O38" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.05</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AG23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK23" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4219,68 +4219,68 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.15</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.38</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.72</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.07</v>
+        <v>1.71</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="O27" t="n">
-        <v>3.38</v>
+        <v>2.4</v>
       </c>
       <c r="P27" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.44</v>
+        <v>3.36</v>
       </c>
       <c r="R27" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="S27" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="T27" t="n">
-        <v>2.65</v>
+        <v>1.85</v>
       </c>
       <c r="U27" t="n">
-        <v>2.9</v>
+        <v>4.4</v>
       </c>
       <c r="V27" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="W27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AD27" t="n">
         <v>1.05</v>
       </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE27" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.86</v>
+        <v>1.47</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.71</v>
+        <v>2.07</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.6</v>
       </c>
-      <c r="O31" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.17</v>
+        <v>2.6</v>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="P34" t="n">
-        <v>13</v>
+        <v>2.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="O39" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="P39" t="n">
-        <v>3.4</v>
+        <v>2.96</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="R39" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="S39" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="T39" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="U39" t="n">
-        <v>4</v>
+        <v>4.45</v>
       </c>
       <c r="V39" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.65</v>
+        <v>6.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE39" t="n">
         <v>1.02</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O40" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="P40" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.08</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,23 +2470,23 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,13 +2495,13 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2513,25 +2513,25 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,23 +2629,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2672,25 +2672,25 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="O15" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="P15" t="n">
-        <v>4.02</v>
+        <v>4.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.43</v>
+        <v>2.34</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>3.34</v>
       </c>
       <c r="U15" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W15" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.38</v>
+        <v>3.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.66</v>
+        <v>1.79</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK15" t="n">
         <v>2</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="O16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>4.41</v>
+        <v>4.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="R16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.34</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.37</v>
-      </c>
       <c r="V16" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.75</v>
+        <v>4.38</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK16" t="n">
         <v>2</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,13 +3587,13 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.07</v>
+        <v>1.61</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,19 +5018,19 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O29" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P29" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R29" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="S29" t="n">
         <v>1.42</v>
@@ -5039,43 +5039,43 @@
         <v>2.65</v>
       </c>
       <c r="U29" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V29" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W29" t="n">
         <v>1.05</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.17</v>
+        <v>2.6</v>
       </c>
       <c r="O33" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="P33" t="n">
-        <v>13</v>
+        <v>2.85</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="O34" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="P34" t="n">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="O37" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="P37" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA37" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.87</v>
-      </c>
       <c r="AB37" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.6</v>
+        <v>2.41</v>
       </c>
       <c r="O39" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="P39" t="n">
-        <v>2.96</v>
+        <v>3.23</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="R39" t="n">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="S39" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="T39" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="U39" t="n">
-        <v>4.45</v>
+        <v>4.05</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X39" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AE39" t="n">
         <v>1.02</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>2.09</v>
       </c>
       <c r="R8" t="n">
-        <v>2.73</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.17</v>
       </c>
-      <c r="T8" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Z8" t="n">
-        <v>7.08</v>
+        <v>5.68</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="AB8" t="n">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="AC8" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.79</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O9" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R9" t="n">
         <v>2.45</v>
       </c>
-      <c r="O9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.46</v>
-      </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="T9" t="n">
-        <v>3.94</v>
+        <v>4.2</v>
       </c>
       <c r="U9" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="V9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W9" t="n">
         <v>1.18</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.57</v>
+        <v>6.18</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF9" t="n">
         <v>1.35</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="O20" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7</v>
+        <v>4.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,13 +3905,13 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="R23" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T23" t="n">
         <v>2.15</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB23" t="n">
         <v>1.38</v>
       </c>
-      <c r="T23" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,80 +4223,80 @@
         </is>
       </c>
       <c r="N24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF24" t="n">
         <v>2.05</v>
       </c>
-      <c r="O24" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P24" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U24" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF24" t="n">
+      <c r="AG24" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK24" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,7 +4340,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,13 +4541,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -4580,10 +4580,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -4817,7 +4817,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.11</v>
+        <v>2.42</v>
       </c>
       <c r="O28" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="P28" t="n">
-        <v>3.68</v>
+        <v>2.57</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,80 +5336,80 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="P31" t="n">
-        <v>4.26</v>
+        <v>2.96</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.66</v>
+        <v>3.6</v>
       </c>
       <c r="R31" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="S31" t="n">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="T31" t="n">
-        <v>2.32</v>
+        <v>1.97</v>
       </c>
       <c r="U31" t="n">
-        <v>2.63</v>
+        <v>4.45</v>
       </c>
       <c r="V31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.39</v>
       </c>
-      <c r="W31" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK31" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O37" t="n">
-        <v>2.58</v>
+        <v>2.75</v>
       </c>
       <c r="P37" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AC37" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="O38" t="n">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="P38" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>2.09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="T7" t="n">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="U7" t="n">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="V7" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="Z7" t="n">
-        <v>6</v>
+        <v>5.68</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.37</v>
+        <v>1.68</v>
       </c>
       <c r="AB7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC7" t="n">
         <v>2.66</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AD7" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG7" t="n">
         <v>2.08</v>
       </c>
-      <c r="AD7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.09</v>
+        <v>1.78</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T8" t="n">
-        <v>3.16</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.39</v>
+        <v>1.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="W8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.08</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Z8" t="n">
-        <v>5.68</v>
+        <v>6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.68</v>
+        <v>1.37</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.21</v>
+        <v>2.66</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.66</v>
+        <v>2.08</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2470,23 +2470,23 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,13 +2495,13 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2513,25 +2513,25 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,23 +2629,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -2672,25 +2672,25 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -3272,13 +3272,13 @@
         <v>2.6</v>
       </c>
       <c r="O18" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="P18" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
         <v>1.72</v>
@@ -3290,28 +3290,28 @@
         <v>2.07</v>
       </c>
       <c r="U18" t="n">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="V18" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
         <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC18" t="n">
         <v>6.2</v>
@@ -3323,7 +3323,7 @@
         <v>1.03</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AG18" t="n">
         <v>1.57</v>
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,80 +4064,80 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.05</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P23" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF23" t="n">
+      <c r="AG23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK23" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.62</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,7 +4181,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="P24" t="n">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="R24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.15</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.38</v>
       </c>
-      <c r="T24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC24" t="n">
-        <v>3.3</v>
+        <v>5.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.73</v>
+        <v>1.54</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,19 +4382,19 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O25" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P25" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R25" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="S25" t="n">
         <v>1.42</v>
@@ -4403,43 +4403,43 @@
         <v>2.65</v>
       </c>
       <c r="U25" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V25" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
         <v>1.05</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,80 +4700,80 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.33</v>
+        <v>2.11</v>
       </c>
       <c r="O27" t="n">
-        <v>2.4</v>
+        <v>3.38</v>
       </c>
       <c r="P27" t="n">
-        <v>3.95</v>
+        <v>3.68</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.36</v>
+        <v>2.44</v>
       </c>
       <c r="R27" t="n">
-        <v>1.6</v>
+        <v>2.03</v>
       </c>
       <c r="S27" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="T27" t="n">
-        <v>1.85</v>
+        <v>2.65</v>
       </c>
       <c r="U27" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="V27" t="n">
-        <v>1.17</v>
+        <v>1.32</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>1.17</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.87</v>
+        <v>3.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>3.67</v>
+        <v>2.15</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC27" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AK27" t="n">
-        <v>1.47</v>
+        <v>1.86</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.6</v>
       </c>
-      <c r="O31" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U31" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>6.9</v>
-      </c>
       <c r="AD31" t="n">
-        <v>1.04</v>
+        <v>1.36</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.46</v>
+        <v>2.18</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5453,7 +5453,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O32" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.17</v>
       </c>
-      <c r="O32" t="n">
-        <v>6</v>
-      </c>
-      <c r="P32" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="T32" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V32" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.05</v>
+        <v>1.78</v>
       </c>
       <c r="Z32" t="n">
-        <v>9</v>
+        <v>2.02</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.21</v>
+        <v>3.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>4</v>
+        <v>1.26</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.53</v>
+        <v>6.9</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.25</v>
+        <v>1.04</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.53</v>
+        <v>1.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.14</v>
+        <v>1.46</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="AK32" t="n">
-        <v>3.65</v>
+        <v>1.38</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="O36" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="P36" t="n">
-        <v>4.31</v>
+        <v>3.2</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.05</v>
+        <v>2.87</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O37" t="n">
+        <v>6</v>
+      </c>
+      <c r="P37" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD37" t="n">
         <v>2.25</v>
       </c>
-      <c r="O37" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.41</v>
+        <v>1.99</v>
       </c>
       <c r="O39" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="P39" t="n">
-        <v>3.23</v>
+        <v>4.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.88</v>
+        <v>2.05</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="AC39" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU42"/>
+  <dimension ref="A1:AU49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1305,7 +1305,7 @@
         <v>0</v>
       </c>
       <c r="AU5" s="3" t="n">
-        <v>46220.35416666666</v>
+        <v>46220.33333333334</v>
       </c>
     </row>
     <row r="6">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46220.35763888889</v>
+        <v>46220.35416666666</v>
       </c>
     </row>
     <row r="8">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="S8" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3.16</v>
       </c>
       <c r="U8" t="n">
-        <v>1.88</v>
+        <v>2.39</v>
       </c>
       <c r="V8" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.37</v>
+        <v>1.64</v>
       </c>
       <c r="AB8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC8" t="n">
         <v>2.66</v>
       </c>
-      <c r="AC8" t="n">
-        <v>2.08</v>
-      </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yunnan Yukun</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>3.9</v>
+        <v>5.36</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>6.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.98</v>
+        <v>1.76</v>
       </c>
       <c r="R9" t="n">
-        <v>2.45</v>
+        <v>2.88</v>
       </c>
       <c r="S9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.18</v>
+        <v>6</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.88</v>
+        <v>2.18</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="AU9" s="3" t="n">
-        <v>46220.375</v>
+        <v>46220.35763888889</v>
       </c>
     </row>
     <row r="10">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Yunnan Yukun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>9.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46220.5</v>
+        <v>46220.375</v>
       </c>
     </row>
     <row r="11">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,19 +2474,19 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -2495,13 +2495,13 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -2513,25 +2513,25 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46220.54166666666</v>
+        <v>46220.5</v>
       </c>
     </row>
     <row r="14">
@@ -2586,27 +2586,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2629,68 +2629,68 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46220.54166666666</v>
+        <v>46220.52083333334</v>
       </c>
     </row>
     <row r="15">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.72</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>4.41</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.37</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>1.49</v>
+        <v>1.95</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.79</v>
+        <v>1.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.92</v>
+        <v>3.45</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.64</v>
+        <v>1.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.38</v>
+        <v>2.02</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46220.58333333334</v>
+        <v>46220.54166666666</v>
       </c>
     </row>
     <row r="16">
@@ -2904,27 +2904,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.78</v>
+        <v>5.8</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="P16" t="n">
-        <v>4.02</v>
+        <v>1.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.41</v>
+        <v>5.45</v>
       </c>
       <c r="R16" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="U16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.34</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AD16" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
         <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.24</v>
+        <v>2.33</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>1.07</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46220.58333333334</v>
+        <v>46220.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -3063,27 +3063,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.16</v>
+        <v>3.63</v>
       </c>
       <c r="O17" t="n">
-        <v>7.6</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.46</v>
+        <v>5.65</v>
       </c>
       <c r="R17" t="n">
-        <v>3.18</v>
+        <v>2.12</v>
       </c>
       <c r="S17" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="T17" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.03</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.25</v>
       </c>
-      <c r="AB17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AK17" t="n">
-        <v>5.4</v>
+        <v>1.15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="AU17" s="3" t="n">
-        <v>46220.59375</v>
+        <v>46220.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -3222,12 +3222,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3372,7 +3372,7 @@
         <v>0</v>
       </c>
       <c r="AU18" s="3" t="n">
-        <v>46220.625</v>
+        <v>46220.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>2.92</v>
+        <v>3.78</v>
       </c>
       <c r="P19" t="n">
-        <v>3.74</v>
+        <v>3.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.79</v>
+        <v>2.33</v>
       </c>
       <c r="R19" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="S19" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.22</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>3.58</v>
+        <v>2.41</v>
       </c>
       <c r="V19" t="n">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.54</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.32</v>
+        <v>4.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.56</v>
+        <v>1.64</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.4</v>
+        <v>2.18</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.05</v>
+        <v>2.63</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.1</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.21</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3531,7 +3531,7 @@
         <v>0</v>
       </c>
       <c r="AU19" s="3" t="n">
-        <v>46220.77083333334</v>
+        <v>46220.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>3.94</v>
       </c>
       <c r="P20" t="n">
-        <v>4.05</v>
+        <v>3.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="R20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.15</v>
       </c>
-      <c r="S20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AC20" t="n">
-        <v>3.75</v>
+        <v>2.77</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.92</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
       <c r="AU20" s="3" t="n">
-        <v>46220.79166666666</v>
+        <v>46220.58333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.99</v>
+        <v>1.14</v>
       </c>
       <c r="O21" t="n">
-        <v>2.93</v>
+        <v>8.6</v>
       </c>
       <c r="P21" t="n">
-        <v>4.35</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.74</v>
+        <v>1.44</v>
       </c>
       <c r="R21" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC21" t="n">
         <v>1.8</v>
       </c>
-      <c r="S21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1.07</v>
+        <v>2.04</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.36</v>
+        <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.77</v>
+        <v>5</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>0</v>
       </c>
       <c r="AU21" s="3" t="n">
-        <v>46220.79166666666</v>
+        <v>46220.59375</v>
       </c>
     </row>
     <row r="22">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3908,61 +3908,61 @@
         <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="AU22" s="3" t="n">
-        <v>46220.79166666666</v>
+        <v>46220.625</v>
       </c>
     </row>
     <row r="23">
@@ -4017,27 +4017,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="AU23" s="3" t="n">
-        <v>46220.8125</v>
+        <v>46220.625</v>
       </c>
     </row>
     <row r="24">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.05</v>
+        <v>2.58</v>
       </c>
       <c r="O24" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="P24" t="n">
-        <v>3.85</v>
+        <v>2.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.88</v>
+        <v>1.72</v>
       </c>
       <c r="S24" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="T24" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="U24" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="V24" t="n">
         <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE24" t="n">
         <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.62</v>
+        <v>1.39</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="AU24" s="3" t="n">
-        <v>46220.8125</v>
+        <v>46220.625</v>
       </c>
     </row>
     <row r="25">
@@ -4335,27 +4335,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="AU25" s="3" t="n">
-        <v>46220.83333333334</v>
+        <v>46220.625</v>
       </c>
     </row>
     <row r="26">
@@ -4494,27 +4494,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>2.33</v>
+        <v>1.3</v>
       </c>
       <c r="O26" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="P26" t="n">
-        <v>3.95</v>
+        <v>7.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.36</v>
+        <v>1.72</v>
       </c>
       <c r="R26" t="n">
-        <v>1.6</v>
+        <v>2.63</v>
       </c>
       <c r="S26" t="n">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="T26" t="n">
-        <v>1.85</v>
+        <v>3.9</v>
       </c>
       <c r="U26" t="n">
-        <v>4.4</v>
+        <v>2.13</v>
       </c>
       <c r="V26" t="n">
-        <v>1.17</v>
+        <v>1.61</v>
       </c>
       <c r="W26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.02</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.17</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.79</v>
+        <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.87</v>
+        <v>4.75</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.67</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>6.55</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.05</v>
+        <v>1.59</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.54</v>
+        <v>1.76</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.47</v>
+        <v>2.99</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4644,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="AU26" s="3" t="n">
-        <v>46220.83333333334</v>
+        <v>46220.63541666666</v>
       </c>
     </row>
     <row r="27">
@@ -4653,27 +4653,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,64 +4700,64 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>2.11</v>
+        <v>1.14</v>
       </c>
       <c r="O27" t="n">
-        <v>3.38</v>
+        <v>6.5</v>
       </c>
       <c r="P27" t="n">
-        <v>3.68</v>
+        <v>13</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.44</v>
+        <v>1.54</v>
       </c>
       <c r="R27" t="n">
-        <v>2.03</v>
+        <v>2.64</v>
       </c>
       <c r="S27" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="T27" t="n">
-        <v>2.65</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>2.9</v>
+        <v>2.29</v>
       </c>
       <c r="V27" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.1</v>
+        <v>4.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.61</v>
+        <v>2.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.9</v>
+        <v>2.33</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.86</v>
+        <v>5</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4803,7 +4803,7 @@
         <v>0</v>
       </c>
       <c r="AU27" s="3" t="n">
-        <v>46220.83333333334</v>
+        <v>46220.63541666666</v>
       </c>
     </row>
     <row r="28">
@@ -4812,27 +4812,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4859,64 +4859,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>2.42</v>
+        <v>1.55</v>
       </c>
       <c r="O28" t="n">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="P28" t="n">
-        <v>2.57</v>
+        <v>4.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.07</v>
+        <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4962,7 +4962,7 @@
         <v>0</v>
       </c>
       <c r="AU28" s="3" t="n">
-        <v>46220.83333333334</v>
+        <v>46220.64583333334</v>
       </c>
     </row>
     <row r="29">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>5.44</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="AU29" s="3" t="n">
-        <v>46220.83333333334</v>
+        <v>46220.75</v>
       </c>
     </row>
     <row r="30">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Atlético Rafaela</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="O30" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P30" t="n">
-        <v>4.81</v>
+        <v>4.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="S30" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="T30" t="n">
-        <v>2.15</v>
+        <v>2.54</v>
       </c>
       <c r="U30" t="n">
-        <v>4.15</v>
+        <v>3.05</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.03</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y30" t="n">
-        <v>1.58</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.92</v>
+        <v>2.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.35</v>
+        <v>1.76</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.41</v>
+        <v>3.75</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.54</v>
+        <v>1.92</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>46220.85416666666</v>
+        <v>46220.79166666666</v>
       </c>
     </row>
     <row r="31">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,80 +5336,80 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.87</v>
+        <v>2.5</v>
       </c>
       <c r="O31" t="n">
         <v>3.1</v>
       </c>
       <c r="P31" t="n">
-        <v>4.26</v>
+        <v>2.81</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="S31" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="T31" t="n">
-        <v>2.32</v>
+        <v>2.6</v>
       </c>
       <c r="U31" t="n">
-        <v>2.63</v>
+        <v>3.3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="W31" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z31" t="n">
         <v>2.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.86</v>
+        <v>1.59</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.36</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AK31" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5439,7 +5439,7 @@
         <v>0</v>
       </c>
       <c r="AU31" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.79166666666</v>
       </c>
     </row>
     <row r="32">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>1.99</v>
       </c>
       <c r="O32" t="n">
-        <v>2.58</v>
+        <v>2.93</v>
       </c>
       <c r="P32" t="n">
-        <v>2.96</v>
+        <v>4.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.6</v>
+        <v>2.74</v>
       </c>
       <c r="R32" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="S32" t="n">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="T32" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="U32" t="n">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="V32" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="W32" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.02</v>
+        <v>2.45</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>6.9</v>
+        <v>5.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.38</v>
+        <v>1.77</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5598,7 +5598,7 @@
         <v>0</v>
       </c>
       <c r="AU32" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.79166666666</v>
       </c>
     </row>
     <row r="33">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.6</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="P33" t="n">
-        <v>2.85</v>
+        <v>3.85</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.8125</v>
       </c>
     </row>
     <row r="34">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.41</v>
+        <v>1.45</v>
       </c>
       <c r="O34" t="n">
-        <v>2.66</v>
+        <v>4.8</v>
       </c>
       <c r="P34" t="n">
-        <v>3.23</v>
+        <v>6.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.1</v>
+        <v>1.85</v>
       </c>
       <c r="R34" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="T34" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="U34" t="n">
-        <v>4.05</v>
+        <v>2.43</v>
       </c>
       <c r="V34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE34" t="n">
         <v>1.16</v>
       </c>
-      <c r="W34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
         <v>0</v>
       </c>
       <c r="AU34" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.8125</v>
       </c>
     </row>
     <row r="35">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="O35" t="n">
-        <v>2.7</v>
+        <v>3.45</v>
       </c>
       <c r="P35" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.4</v>
+        <v>2.09</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="AU35" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.83333333334</v>
       </c>
     </row>
     <row r="36">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="P36" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.87</v>
+        <v>3.28</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
       <c r="AU36" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.83333333334</v>
       </c>
     </row>
     <row r="37">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="AU37" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.83333333334</v>
       </c>
     </row>
     <row r="38">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,43 +6449,43 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.45</v>
+        <v>2.15</v>
       </c>
       <c r="O38" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="P38" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>3.4</v>
@@ -6494,19 +6494,19 @@
         <v>1.33</v>
       </c>
       <c r="AC38" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6552,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="AU38" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.83333333334</v>
       </c>
     </row>
     <row r="39">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.99</v>
+        <v>2.11</v>
       </c>
       <c r="O39" t="n">
-        <v>2.95</v>
+        <v>3.38</v>
       </c>
       <c r="P39" t="n">
-        <v>4.31</v>
+        <v>3.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="AU39" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.83333333334</v>
       </c>
     </row>
     <row r="40">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -6870,7 +6870,7 @@
         <v>0</v>
       </c>
       <c r="AU40" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.83333333334</v>
       </c>
     </row>
     <row r="41">
@@ -6879,12 +6879,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Atlético Rafaela</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6926,64 +6926,64 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.37</v>
+        <v>1.83</v>
       </c>
       <c r="O41" t="n">
-        <v>5.31</v>
+        <v>2.9</v>
       </c>
       <c r="P41" t="n">
-        <v>8.65</v>
+        <v>4.81</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="R41" t="n">
-        <v>2.3</v>
+        <v>1.76</v>
       </c>
       <c r="S41" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="T41" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>2.55</v>
+        <v>4.15</v>
       </c>
       <c r="V41" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="W41" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.26</v>
+        <v>2.11</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.57</v>
+        <v>2.92</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.25</v>
+        <v>1.31</v>
       </c>
       <c r="AC41" t="n">
-        <v>2.75</v>
+        <v>6.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.4</v>
+        <v>1.06</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.16</v>
+        <v>1.02</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.83</v>
+        <v>2.54</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>1.15</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.65</v>
+        <v>1.79</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="AU41" s="3" t="n">
-        <v>46220.88194444445</v>
+        <v>46220.85416666666</v>
       </c>
     </row>
     <row r="42">
@@ -7038,156 +7038,1269 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P42" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" s="3" t="n">
+        <v>46220.875</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Delfin SC</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O43" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" s="3" t="n">
+        <v>46220.875</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Argentina Prim B Nacional</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Club Atlético Mitre</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Racing Córdoba</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P44" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" s="3" t="n">
+        <v>46220.875</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="P45" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" s="3" t="n">
+        <v>46220.875</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Kansas City</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P46" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" s="3" t="n">
+        <v>46220.875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O47" t="n">
+        <v>6</v>
+      </c>
+      <c r="P47" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="T47" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V47" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W47" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ47" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" s="3" t="n">
+        <v>46220.875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>USA MLS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="P48" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" s="3" t="n">
+        <v>46220.88194444445</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>23:25</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>USA MLS</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>LA Galaxy</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Los Angeles FC</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="inlineStr">
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N42" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O42" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="P42" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="S42" t="n">
+      <c r="N49" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S49" t="n">
         <v>1.25</v>
       </c>
-      <c r="T42" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="U42" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="V42" t="n">
+      <c r="T49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="V49" t="n">
         <v>1.58</v>
       </c>
-      <c r="W42" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X42" t="n">
+      <c r="W49" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X49" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Y49" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z42" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AA42" t="n">
+      <c r="Z49" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD49" t="n">
         <v>1.55</v>
       </c>
-      <c r="AB42" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AK42" t="n">
+      <c r="AE49" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ49" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK49" t="n">
         <v>1.4</v>
       </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" s="3" t="n">
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" s="3" t="n">
         <v>46220.97569444445</v>
       </c>
     </row>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>3.63</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="P15" t="n">
-        <v>9.199999999999999</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.61</v>
+        <v>5.65</v>
       </c>
       <c r="R15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.2</v>
       </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
       <c r="AA15" t="n">
-        <v>1.23</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.45</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.65</v>
+        <v>3.08</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.43</v>
+        <v>1.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.3</v>
+        <v>1.15</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.63</v>
+        <v>5.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.28</v>
+        <v>3.98</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.65</v>
+        <v>5.45</v>
       </c>
       <c r="R17" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="U17" t="n">
-        <v>2.65</v>
+        <v>2.25</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>2.21</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.08</v>
+        <v>2.34</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>2.33</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,23 +3265,23 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,13 +3290,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -3308,25 +3308,25 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="S24" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="T24" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="U24" t="n">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.81</v>
+        <v>3.56</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.2</v>
+        <v>6.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.6</v>
+        <v>1.46</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="O31" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="P31" t="n">
-        <v>2.81</v>
+        <v>4.35</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="S31" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="T31" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="U31" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="V31" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.4</v>
+        <v>1.52</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.18</v>
+        <v>3.03</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AE31" t="n">
         <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.78</v>
+        <v>1.58</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>1.36</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="P32" t="n">
-        <v>4.35</v>
+        <v>2.81</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="T32" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="U32" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W32" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.03</v>
+        <v>2.18</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.33</v>
+        <v>1.59</v>
       </c>
       <c r="AC32" t="n">
-        <v>5.4</v>
+        <v>4.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AE32" t="n">
         <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>1.36</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.89</v>
+        <v>2.15</v>
       </c>
       <c r="O35" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AC35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,13 +6449,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="P38" t="n">
-        <v>3.5</v>
+        <v>2.57</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -6488,10 +6488,10 @@
         <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.4</v>
+        <v>1.72</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,77 +6608,77 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O39" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P39" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T39" t="n">
         <v>2.56</v>
       </c>
-      <c r="R39" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T39" t="n">
-        <v>2.53</v>
-      </c>
       <c r="U39" t="n">
-        <v>3.11</v>
+        <v>2.77</v>
       </c>
       <c r="V39" t="n">
         <v>1.36</v>
       </c>
       <c r="W39" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.33</v>
       </c>
       <c r="AK39" t="n">
         <v>1.83</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O40" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P40" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.99</v>
+        <v>1.17</v>
       </c>
       <c r="O42" t="n">
-        <v>2.95</v>
+        <v>6</v>
       </c>
       <c r="P42" t="n">
-        <v>4.31</v>
+        <v>13</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.05</v>
+        <v>1.21</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.66</v>
+        <v>3.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="O43" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P43" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="O44" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="P44" t="n">
-        <v>3.2</v>
+        <v>2.85</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.37</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
-        <v>2.9</v>
+        <v>4.31</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="O46" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
         <v>3.1</v>
       </c>
-      <c r="P46" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R46" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="S46" t="n">
+      <c r="AB46" t="n">
         <v>1.36</v>
       </c>
-      <c r="T46" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U46" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC46" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.17</v>
+        <v>1.87</v>
       </c>
       <c r="O47" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>4.26</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="R47" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="S47" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="T47" t="n">
-        <v>5.5</v>
+        <v>2.83</v>
       </c>
       <c r="U47" t="n">
-        <v>1.62</v>
+        <v>2.69</v>
       </c>
       <c r="V47" t="n">
-        <v>2.15</v>
+        <v>1.41</v>
       </c>
       <c r="W47" t="n">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="Z47" t="n">
-        <v>7.5</v>
+        <v>2.75</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="AB47" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.19</v>
+        <v>1.29</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.51</v>
+        <v>1.05</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.19</v>
+        <v>1.99</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AK47" t="n">
-        <v>4.1</v>
+        <v>1.45</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1211,55 +1211,55 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1697,7 +1697,7 @@
         <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="U8" t="n">
         <v>2.39</v>
@@ -1715,7 +1715,7 @@
         <v>1.15</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="AA8" t="n">
         <v>1.64</v>
@@ -1724,13 +1724,13 @@
         <v>2.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="AD8" t="n">
         <v>1.44</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
         <v>1.7</v>
@@ -1752,7 +1752,7 @@
         <v>1.24</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2000,16 +2000,16 @@
         <v>2.62</v>
       </c>
       <c r="O10" t="n">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="R10" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
         <v>1.19</v>
@@ -2018,10 +2018,10 @@
         <v>4.8</v>
       </c>
       <c r="U10" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="V10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W10" t="n">
         <v>1.18</v>
@@ -2030,19 +2030,19 @@
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.75</v>
+        <v>9.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.22</v>
+        <v>2.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
         <v>1.8</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2639,7 +2639,7 @@
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
         <v>3.1</v>
@@ -2651,31 +2651,31 @@
         <v>1.44</v>
       </c>
       <c r="T14" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
         <v>3.2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
         <v>2.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AC14" t="n">
         <v>4.2</v>
@@ -2687,7 +2687,7 @@
         <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
         <v>1.8</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2788,68 +2788,68 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.57</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.8</v>
+        <v>1.28</v>
       </c>
       <c r="O17" t="n">
-        <v>3.98</v>
+        <v>5</v>
       </c>
       <c r="P17" t="n">
-        <v>1.48</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.45</v>
+        <v>1.61</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3</v>
+        <v>3.2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.25</v>
+        <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.53</v>
+        <v>1.23</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.21</v>
+        <v>3.45</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.34</v>
+        <v>1.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>2.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.07</v>
+        <v>3.3</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.28</v>
+        <v>3.63</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="P18" t="n">
-        <v>9.199999999999999</v>
+        <v>2.03</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="R18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3.2</v>
       </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W18" t="n">
+      <c r="AA18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD18" t="n">
         <v>1.27</v>
       </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.43</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.3</v>
+        <v>1.15</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3431,28 +3431,28 @@
         <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>3.78</v>
+        <v>3.94</v>
       </c>
       <c r="P19" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="R19" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="U19" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W19" t="n">
         <v>1.08</v>
@@ -3461,31 +3461,31 @@
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.16</v>
       </c>
-      <c r="Z19" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3590,28 +3590,28 @@
         <v>1.81</v>
       </c>
       <c r="O20" t="n">
-        <v>3.94</v>
+        <v>3.78</v>
       </c>
       <c r="P20" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="R20" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T20" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="V20" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
@@ -3620,31 +3620,31 @@
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="O26" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="P26" t="n">
-        <v>7.65</v>
+        <v>13</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="S26" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T26" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="U26" t="n">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="V26" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,31 +4700,31 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="O27" t="n">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.54</v>
+        <v>1.76</v>
       </c>
       <c r="R27" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="S27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U27" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W27" t="n">
         <v>1.14</v>
@@ -4733,31 +4733,31 @@
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.45</v>
+        <v>1.95</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>5</v>
+        <v>2.99</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="O28" t="n">
-        <v>3.75</v>
+        <v>4.05</v>
       </c>
       <c r="P28" t="n">
-        <v>4.55</v>
+        <v>4.89</v>
       </c>
       <c r="Q28" t="n">
         <v>2.12</v>
@@ -4874,49 +4874,49 @@
         <v>2.25</v>
       </c>
       <c r="S28" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T28" t="n">
-        <v>3.2</v>
+        <v>2.99</v>
       </c>
       <c r="U28" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="V28" t="n">
         <v>1.42</v>
       </c>
       <c r="W28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
         <v>1.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB28" t="n">
         <v>1.85</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE28" t="n">
         <v>1.07</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="O30" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P30" t="n">
-        <v>4.05</v>
+        <v>2.81</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R30" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S30" t="n">
         <v>1.44</v>
       </c>
       <c r="T30" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="U30" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="V30" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X30" t="n">
         <v>1.05</v>
       </c>
-      <c r="X30" t="n">
+      <c r="Y30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y30" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AF30" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="O32" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P32" t="n">
-        <v>2.81</v>
+        <v>4.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S32" t="n">
         <v>1.44</v>
       </c>
       <c r="T32" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="U32" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="V32" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
         <v>1.03</v>
       </c>
-      <c r="X32" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y32" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5813,7 +5813,7 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
         <v>4.8</v>
@@ -5834,7 +5834,7 @@
         <v>3.6</v>
       </c>
       <c r="U34" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="V34" t="n">
         <v>1.57</v>
@@ -5861,7 +5861,7 @@
         <v>2.65</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AE34" t="n">
         <v>1.16</v>
@@ -5886,7 +5886,7 @@
         <v>1.16</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.7</v>
+        <v>2.79</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,65 +6131,65 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O36" t="n">
-        <v>2.45</v>
+        <v>3.38</v>
       </c>
       <c r="P36" t="n">
-        <v>3.85</v>
+        <v>3.68</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.32</v>
+        <v>2.56</v>
       </c>
       <c r="R36" t="n">
-        <v>1.61</v>
+        <v>2.19</v>
       </c>
       <c r="S36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG36" t="n">
         <v>1.83</v>
       </c>
-      <c r="T36" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AH36" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,13 +6290,13 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -6329,10 +6329,10 @@
         <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="O38" t="n">
-        <v>3.22</v>
+        <v>2.45</v>
       </c>
       <c r="P38" t="n">
-        <v>2.57</v>
+        <v>3.85</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.72</v>
+        <v>3.28</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.07</v>
+        <v>1.3</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>2.1</v>
       </c>
       <c r="S39" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="T39" t="n">
         <v>2.56</v>
@@ -6638,19 +6638,19 @@
         <v>1.07</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
         <v>1.33</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA39" t="n">
         <v>2.09</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC39" t="n">
         <v>3.5</v>
@@ -6662,10 +6662,10 @@
         <v>1.07</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="O40" t="n">
-        <v>3.38</v>
+        <v>2.7</v>
       </c>
       <c r="P40" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.12</v>
+        <v>3.4</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.17</v>
+        <v>1.99</v>
       </c>
       <c r="O42" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="P42" t="n">
-        <v>13</v>
+        <v>4.31</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O43" t="n">
-        <v>2.87</v>
+        <v>2.65</v>
       </c>
       <c r="P43" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
         <v>3.1</v>
       </c>
-      <c r="R43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AB43" t="n">
-        <v>1.55</v>
+        <v>1.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="O45" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P45" t="n">
-        <v>4.31</v>
+        <v>2.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.35</v>
+        <v>1.17</v>
       </c>
       <c r="O46" t="n">
-        <v>2.65</v>
+        <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>3.2</v>
+        <v>13</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>3.1</v>
+        <v>1.21</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.36</v>
+        <v>3.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8039,16 +8039,16 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="O48" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="P48" t="n">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="R48" t="n">
         <v>2.4</v>
@@ -8057,16 +8057,16 @@
         <v>1.3</v>
       </c>
       <c r="T48" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="U48" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V48" t="n">
         <v>1.5</v>
       </c>
       <c r="W48" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X48" t="n">
         <v>1.04</v>
@@ -8075,28 +8075,28 @@
         <v>1.22</v>
       </c>
       <c r="Z48" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA48" t="n">
         <v>1.66</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>1.07</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="O49" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P49" t="n">
         <v>2.3</v>
@@ -8210,19 +8210,19 @@
         <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S49" t="n">
         <v>1.25</v>
       </c>
       <c r="T49" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="U49" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V49" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W49" t="n">
         <v>1.15</v>
@@ -8231,28 +8231,28 @@
         <v>1.03</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AA49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD49" t="n">
         <v>1.52</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.55</v>
       </c>
       <c r="AE49" t="n">
         <v>1.18</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG49" t="n">
         <v>2.6</v>
@@ -8268,7 +8268,7 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AK49" t="n">
         <v>1.4</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1226,7 +1226,7 @@
         <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
         <v>1.11</v>
@@ -1235,7 +1235,7 @@
         <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
         <v>4.2</v>
@@ -1244,22 +1244,22 @@
         <v>1.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC5" t="n">
         <v>2.57</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE5" t="n">
         <v>1.14</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.2</v>
+        <v>1.95</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1688,55 +1688,55 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U8" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.15</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
         <v>1.7</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1847,19 +1847,19 @@
         <v>6.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T9" t="n">
         <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="V9" t="n">
         <v>1.73</v>
@@ -1871,31 +1871,31 @@
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.62</v>
+        <v>3.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AE9" t="n">
         <v>1.29</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.17</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2009,13 +2009,13 @@
         <v>2.99</v>
       </c>
       <c r="R10" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S10" t="n">
         <v>1.19</v>
       </c>
       <c r="T10" t="n">
-        <v>4.8</v>
+        <v>3.86</v>
       </c>
       <c r="U10" t="n">
         <v>1.99</v>
@@ -2036,13 +2036,13 @@
         <v>9.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AB10" t="n">
         <v>2.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD10" t="n">
         <v>1.8</v>
@@ -2051,10 +2051,10 @@
         <v>1.34</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,65 +2951,65 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.64</v>
+        <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.5</v>
       </c>
-      <c r="Q16" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="R16" t="n">
+      <c r="AG16" t="n">
         <v>2.32</v>
       </c>
-      <c r="S16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.08</v>
+        <v>3.3</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>3.63</v>
       </c>
       <c r="O17" t="n">
-        <v>5</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>9.199999999999999</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.61</v>
+        <v>5.6</v>
       </c>
       <c r="R17" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
         <v>3.2</v>
       </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="W17" t="n">
+      <c r="AA17" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.27</v>
       </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.02</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.43</v>
+        <v>1.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.32</v>
+        <v>1.81</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.3</v>
+        <v>1.15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,80 +3269,80 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>3.63</v>
+        <v>5.64</v>
       </c>
       <c r="O18" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="R18" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S18" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="U18" t="n">
-        <v>2.73</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,31 +3428,31 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="O19" t="n">
-        <v>3.94</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>3.65</v>
+        <v>3.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="R19" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T19" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U19" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="V19" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.08</v>
@@ -3461,31 +3461,31 @@
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.77</v>
+        <v>2.51</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.43</v>
+        <v>2.3</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="U20" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AC20" t="n">
         <v>2.63</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,19 +3746,19 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="O21" t="n">
-        <v>8.6</v>
+        <v>7.7</v>
       </c>
       <c r="P21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="R21" t="n">
-        <v>3.46</v>
+        <v>3.3</v>
       </c>
       <c r="S21" t="n">
         <v>1.14</v>
@@ -3767,13 +3767,13 @@
         <v>4.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
@@ -3782,28 +3782,28 @@
         <v>1.03</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AK21" t="n">
-        <v>5</v>
+        <v>4.44</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4385,22 +4385,22 @@
         <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="P25" t="n">
         <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="R25" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="S25" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="T25" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U25" t="n">
         <v>4.5</v>
@@ -4412,7 +4412,7 @@
         <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Y25" t="n">
         <v>1.76</v>
@@ -4421,13 +4421,13 @@
         <v>1.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.56</v>
+        <v>3.28</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC25" t="n">
-        <v>6.95</v>
+        <v>7</v>
       </c>
       <c r="AD25" t="n">
         <v>1.04</v>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5027,22 +5027,22 @@
         <v>3.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R29" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S29" t="n">
         <v>1.53</v>
       </c>
       <c r="T29" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="U29" t="n">
         <v>3.58</v>
       </c>
       <c r="V29" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W29" t="n">
         <v>1.04</v>
@@ -5063,7 +5063,7 @@
         <v>1.4</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.44</v>
+        <v>5.05</v>
       </c>
       <c r="AD29" t="n">
         <v>1.1</v>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.5</v>
+        <v>1.99</v>
       </c>
       <c r="O30" t="n">
-        <v>3.1</v>
+        <v>2.93</v>
       </c>
       <c r="P30" t="n">
-        <v>2.81</v>
+        <v>4.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S30" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="T30" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="U30" t="n">
-        <v>3.3</v>
+        <v>4.4</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.18</v>
+        <v>3.07</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AC30" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AE30" t="n">
         <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.9</v>
+        <v>2.38</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.78</v>
+        <v>1.52</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,80 +5336,80 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.99</v>
+        <v>2.47</v>
       </c>
       <c r="O31" t="n">
-        <v>2.93</v>
+        <v>3.06</v>
       </c>
       <c r="P31" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.74</v>
+        <v>3.22</v>
       </c>
       <c r="R31" t="n">
-        <v>1.8</v>
+        <v>2.06</v>
       </c>
       <c r="S31" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="T31" t="n">
-        <v>2.25</v>
+        <v>2.47</v>
       </c>
       <c r="U31" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="V31" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="W31" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.45</v>
+        <v>2.83</v>
       </c>
       <c r="AA31" t="n">
-        <v>3.03</v>
+        <v>2.32</v>
       </c>
       <c r="AB31" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AK31" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5504,16 +5504,16 @@
         <v>4.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.45</v>
+        <v>2.57</v>
       </c>
       <c r="R32" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="S32" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="T32" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
         <v>3.05</v>
@@ -5522,7 +5522,7 @@
         <v>1.32</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X32" t="n">
         <v>1.03</v>
@@ -5534,19 +5534,19 @@
         <v>2.83</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.75</v>
+        <v>3.99</v>
       </c>
       <c r="AD32" t="n">
         <v>1.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF32" t="n">
         <v>1.92</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="O33" t="n">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="P33" t="n">
-        <v>3.85</v>
+        <v>6.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="R33" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="S33" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="T33" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="U33" t="n">
-        <v>3.98</v>
+        <v>2.31</v>
       </c>
       <c r="V33" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="W33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X33" t="n">
         <v>1.01</v>
       </c>
-      <c r="X33" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.23</v>
+        <v>4.75</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.89</v>
+        <v>1.63</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.8</v>
+        <v>2.65</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.07</v>
+        <v>1.51</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.54</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.62</v>
+        <v>2.79</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="O34" t="n">
-        <v>4.8</v>
+        <v>2.84</v>
       </c>
       <c r="P34" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="S34" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>2.24</v>
       </c>
       <c r="U34" t="n">
-        <v>2.31</v>
+        <v>3.95</v>
       </c>
       <c r="V34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.57</v>
       </c>
-      <c r="W34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z34" t="n">
-        <v>4.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.63</v>
+        <v>2.74</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.65</v>
+        <v>5.85</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.51</v>
+        <v>1.12</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.98</v>
+        <v>1.54</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.79</v>
+        <v>1.62</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="O38" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="P38" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.32</v>
+        <v>2.4</v>
       </c>
       <c r="R38" t="n">
-        <v>1.61</v>
+        <v>2.1</v>
       </c>
       <c r="S38" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK38" t="n">
         <v>1.83</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U38" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.44</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="O39" t="n">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB39" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z39" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="P40" t="n">
         <v>3.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6938,7 +6938,7 @@
         <v>2.6</v>
       </c>
       <c r="R41" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="S41" t="n">
         <v>1.57</v>
@@ -6947,7 +6947,7 @@
         <v>2.25</v>
       </c>
       <c r="U41" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
         <v>1.16</v>
@@ -6959,7 +6959,7 @@
         <v>1.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Z41" t="n">
         <v>2.11</v>
@@ -6968,7 +6968,7 @@
         <v>2.92</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AC41" t="n">
         <v>6.15</v>
@@ -6996,7 +6996,7 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AK41" t="n">
         <v>1.79</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,13 +7085,13 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="O42" t="n">
         <v>2.95</v>
       </c>
       <c r="P42" t="n">
-        <v>4.31</v>
+        <v>2.85</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -7124,10 +7124,10 @@
         <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
         <v>0</v>
@@ -7244,13 +7244,13 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O43" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="P43" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.6</v>
+        <v>1.17</v>
       </c>
       <c r="O44" t="n">
-        <v>2.95</v>
+        <v>6</v>
       </c>
       <c r="P44" t="n">
-        <v>2.85</v>
+        <v>13</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.37</v>
+        <v>1.87</v>
       </c>
       <c r="O45" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="P45" t="n">
-        <v>2.9</v>
+        <v>4.26</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="R45" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="S45" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="T45" t="n">
-        <v>2.34</v>
+        <v>2.83</v>
       </c>
       <c r="U45" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="V45" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD45" t="n">
         <v>1.29</v>
       </c>
-      <c r="W45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB45" t="n">
+      <c r="AE45" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF45" t="n">
         <v>1.55</v>
       </c>
-      <c r="AC45" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG45" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,80 +7721,80 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>3.02</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>3.1</v>
       </c>
       <c r="Q46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AK46" t="n">
         <v>1.53</v>
-      </c>
-      <c r="R46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="T46" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="V46" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>4.1</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="O47" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P47" t="n">
-        <v>4.26</v>
+        <v>4.31</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AB47" t="n">
         <v>1.66</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2788,68 +2788,68 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.63</v>
+        <v>5.64</v>
       </c>
       <c r="O17" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.6</v>
+        <v>5.57</v>
       </c>
       <c r="R17" t="n">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="U17" t="n">
-        <v>2.73</v>
+        <v>2.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.64</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,31 +4541,31 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="O26" t="n">
-        <v>6.5</v>
+        <v>4.95</v>
       </c>
       <c r="P26" t="n">
-        <v>13</v>
+        <v>6.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="S26" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T26" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="U26" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W26" t="n">
         <v>1.14</v>
@@ -4574,31 +4574,31 @@
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
         <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK26" t="n">
-        <v>5</v>
+        <v>2.99</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,31 +4700,31 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="O27" t="n">
-        <v>4.95</v>
+        <v>6.5</v>
       </c>
       <c r="P27" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="R27" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="S27" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T27" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V27" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
         <v>1.14</v>
@@ -4733,31 +4733,31 @@
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD27" t="n">
         <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>2.63</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O30" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="P30" t="n">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.98</v>
+        <v>2.57</v>
       </c>
       <c r="R30" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="S30" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="T30" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="U30" t="n">
-        <v>4.4</v>
+        <v>3.05</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X30" t="n">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.3</v>
+        <v>3.99</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AE30" t="n">
         <v>1.03</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.52</v>
+        <v>1.86</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="O32" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="P32" t="n">
-        <v>4.05</v>
+        <v>4.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.57</v>
+        <v>2.98</v>
       </c>
       <c r="R32" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="S32" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U32" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z32" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AC32" t="n">
-        <v>3.99</v>
+        <v>5.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="AE32" t="n">
         <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.86</v>
+        <v>1.52</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="P36" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.56</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>2.19</v>
+        <v>1.62</v>
       </c>
       <c r="S36" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="T36" t="n">
-        <v>2.53</v>
+        <v>1.87</v>
       </c>
       <c r="U36" t="n">
-        <v>3.11</v>
+        <v>4.5</v>
       </c>
       <c r="V36" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="W36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD36" t="n">
         <v>1.05</v>
       </c>
-      <c r="X36" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>2.54</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.83</v>
+        <v>1.45</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="O40" t="n">
-        <v>2.45</v>
+        <v>3.38</v>
       </c>
       <c r="P40" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="R40" t="n">
-        <v>1.62</v>
+        <v>2.19</v>
       </c>
       <c r="S40" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="T40" t="n">
-        <v>1.87</v>
+        <v>2.53</v>
       </c>
       <c r="U40" t="n">
-        <v>4.5</v>
+        <v>3.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X40" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.99</v>
+        <v>3.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.2</v>
+        <v>2.14</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.5</v>
+        <v>3.78</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.54</v>
+        <v>1.91</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.17</v>
+        <v>1.99</v>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>4.31</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,80 +7562,80 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="O45" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="P45" t="n">
         <v>3.1</v>
       </c>
-      <c r="P45" t="n">
-        <v>4.26</v>
-      </c>
       <c r="Q45" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="R45" t="n">
-        <v>2.1</v>
+        <v>1.89</v>
       </c>
       <c r="S45" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U45" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45" t="n">
         <v>1.34</v>
       </c>
-      <c r="T45" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U45" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AK45" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="O46" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="P46" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="R46" t="n">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="S46" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="T46" t="n">
-        <v>2.39</v>
+        <v>2.83</v>
       </c>
       <c r="U46" t="n">
-        <v>3.4</v>
+        <v>2.69</v>
       </c>
       <c r="V46" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AD46" t="n">
         <v>1.29</v>
       </c>
-      <c r="W46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB46" t="n">
+      <c r="AE46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF46" t="n">
         <v>1.55</v>
       </c>
-      <c r="AC46" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AG46" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.34</v>
+        <v>1.1</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.99</v>
+        <v>1.17</v>
       </c>
       <c r="O47" t="n">
-        <v>2.95</v>
+        <v>6</v>
       </c>
       <c r="P47" t="n">
-        <v>4.31</v>
+        <v>13</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.05</v>
+        <v>1.21</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.66</v>
+        <v>3.5</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.63</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.6</v>
+        <v>1.61</v>
       </c>
       <c r="R15" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.73</v>
+        <v>1.74</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.93</v>
+        <v>1.23</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>3.45</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.14</v>
+        <v>1.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>2.02</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>1.43</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.81</v>
+        <v>2.32</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.15</v>
+        <v>3.3</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="O16" t="n">
+        <v>4</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="R16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S16" t="n">
         <v>1.28</v>
       </c>
-      <c r="O16" t="n">
-        <v>5</v>
-      </c>
-      <c r="P16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.45</v>
+        <v>2.36</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.3</v>
+        <v>1.08</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.64</v>
+        <v>3.63</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="U17" t="n">
-        <v>2.34</v>
+        <v>2.73</v>
       </c>
       <c r="V17" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.29</v>
+        <v>3.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U19" t="n">
         <v>2.39</v>
       </c>
-      <c r="R19" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.41</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
         <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AD19" t="n">
         <v>1.42</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
         <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3</v>
+        <v>2.43</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T20" t="n">
-        <v>3.34</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AD20" t="n">
         <v>1.42</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF20" t="n">
         <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4226,61 +4226,61 @@
         <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="P24" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.66</v>
       </c>
       <c r="R24" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="S24" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="T24" t="n">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="U24" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.78</v>
+        <v>3.28</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>6.17</v>
+        <v>7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,80 +5177,80 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="O30" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U30" t="n">
         <v>3.3</v>
       </c>
-      <c r="P30" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U30" t="n">
-        <v>3.05</v>
-      </c>
       <c r="V30" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="W30" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
         <v>1.03</v>
       </c>
       <c r="Y30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ30" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z30" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK30" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.47</v>
+        <v>1.99</v>
       </c>
       <c r="O31" t="n">
-        <v>3.06</v>
+        <v>2.93</v>
       </c>
       <c r="P31" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="R31" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="S31" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="T31" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="U31" t="n">
-        <v>3.4</v>
+        <v>3.98</v>
       </c>
       <c r="V31" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,80 +5495,80 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O32" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="P32" t="n">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.98</v>
+        <v>2.57</v>
       </c>
       <c r="R32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.85</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.67</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="O33" t="n">
-        <v>4.8</v>
+        <v>2.84</v>
       </c>
       <c r="P33" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="R33" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="S33" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="T33" t="n">
-        <v>3.6</v>
+        <v>2.24</v>
       </c>
       <c r="U33" t="n">
-        <v>2.31</v>
+        <v>3.95</v>
       </c>
       <c r="V33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y33" t="n">
         <v>1.57</v>
       </c>
-      <c r="W33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z33" t="n">
-        <v>4.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.63</v>
+        <v>2.74</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.2</v>
+        <v>1.39</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.65</v>
+        <v>5.85</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.51</v>
+        <v>1.12</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.98</v>
+        <v>1.54</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.79</v>
+        <v>1.62</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>2.84</v>
+        <v>4.8</v>
       </c>
       <c r="P34" t="n">
-        <v>3.85</v>
+        <v>6.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.88</v>
+        <v>1.85</v>
       </c>
       <c r="R34" t="n">
-        <v>1.78</v>
+        <v>2.5</v>
       </c>
       <c r="S34" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="T34" t="n">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="U34" t="n">
-        <v>3.95</v>
+        <v>2.31</v>
       </c>
       <c r="V34" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="W34" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X34" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="Z34" t="n">
-        <v>2.25</v>
+        <v>4.75</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.74</v>
+        <v>1.63</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.39</v>
+        <v>2.2</v>
       </c>
       <c r="AC34" t="n">
-        <v>5.85</v>
+        <v>2.65</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.12</v>
+        <v>1.51</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>1.72</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.54</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.62</v>
+        <v>2.79</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="O36" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="P36" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC36" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q36" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R36" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U36" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>6.5</v>
-      </c>
       <c r="AD36" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.54</v>
+        <v>1.84</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O37" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P37" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="O38" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
-        <v>3.38</v>
+        <v>2.62</v>
       </c>
       <c r="P40" t="n">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB40" t="n">
         <v>1.33</v>
       </c>
-      <c r="W40" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC40" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="O43" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="P43" t="n">
-        <v>3.1</v>
+        <v>4.26</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA43" t="n">
-        <v>3.1</v>
+        <v>1.84</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.36</v>
+        <v>1.97</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.99</v>
+        <v>2.25</v>
       </c>
       <c r="O44" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>4.31</v>
+        <v>3.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.66</v>
+        <v>1.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
-        <v>3.02</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
-        <v>3.1</v>
+        <v>4.31</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.87</v>
+        <v>1.17</v>
       </c>
       <c r="O46" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>4.26</v>
+        <v>13</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.85</v>
+        <v>1.53</v>
       </c>
       <c r="R46" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="S46" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="T46" t="n">
-        <v>2.83</v>
+        <v>5.5</v>
       </c>
       <c r="U46" t="n">
-        <v>2.69</v>
+        <v>1.62</v>
       </c>
       <c r="V46" t="n">
-        <v>1.41</v>
+        <v>2.15</v>
       </c>
       <c r="W46" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.28</v>
+        <v>7.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.84</v>
+        <v>1.21</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.97</v>
+        <v>3.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>3.04</v>
+        <v>1.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.29</v>
+        <v>2.19</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.08</v>
+        <v>1.51</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.17</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
-        <v>6</v>
+        <v>2.66</v>
       </c>
       <c r="P47" t="n">
-        <v>13</v>
+        <v>3.1</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.21</v>
+        <v>3.1</v>
       </c>
       <c r="AB47" t="n">
-        <v>3.5</v>
+        <v>1.36</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.99</v>
+        <v>1.75</v>
       </c>
       <c r="R8" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.19</v>
       </c>
       <c r="T8" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U8" t="n">
-        <v>2.36</v>
+        <v>2.03</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="W8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.08</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z8" t="n">
-        <v>4.39</v>
+        <v>6.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.23</v>
+        <v>3.16</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.66</v>
+        <v>2.02</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>2.96</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="S9" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U9" t="n">
-        <v>2.03</v>
+        <v>2.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>6.5</v>
+        <v>4.39</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.16</v>
+        <v>2.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.96</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
+        <v>5.64</v>
+      </c>
+      <c r="O15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S15" t="n">
         <v>1.28</v>
       </c>
-      <c r="O15" t="n">
-        <v>5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U15" t="n">
-        <v>1.74</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="W15" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.23</v>
+        <v>1.56</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.45</v>
+        <v>2.36</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.65</v>
+        <v>2.29</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.02</v>
+        <v>1.54</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.43</v>
+        <v>1.2</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.3</v>
+        <v>1.08</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.64</v>
+        <v>3.63</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.57</v>
+        <v>5.6</v>
       </c>
       <c r="R16" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T16" t="n">
-        <v>3.18</v>
+        <v>2.9</v>
       </c>
       <c r="U16" t="n">
-        <v>2.34</v>
+        <v>2.73</v>
       </c>
       <c r="V16" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.36</v>
+        <v>1.75</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.29</v>
+        <v>3.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,23 +3265,23 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,13 +3290,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -3308,25 +3308,25 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3749,43 +3749,43 @@
         <v>1.15</v>
       </c>
       <c r="O21" t="n">
-        <v>7.7</v>
+        <v>8.65</v>
       </c>
       <c r="P21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R21" t="n">
         <v>3.3</v>
       </c>
       <c r="S21" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="T21" t="n">
         <v>4.8</v>
       </c>
       <c r="U21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V21" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="W21" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AB21" t="n">
         <v>3.6</v>
@@ -3800,10 +3800,10 @@
         <v>1.44</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AK21" t="n">
-        <v>4.44</v>
+        <v>4.75</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3914,10 +3914,10 @@
         <v>2.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>3.48</v>
       </c>
       <c r="R22" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="S22" t="n">
         <v>1.67</v>
@@ -3944,25 +3944,25 @@
         <v>2.19</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="AB22" t="n">
         <v>1.36</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.17</v>
+        <v>5.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE22" t="n">
         <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3978,7 +3978,7 @@
         <v>1.37</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5018,19 +5018,19 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O29" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="P29" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="R29" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="S29" t="n">
         <v>1.53</v>
@@ -5039,7 +5039,7 @@
         <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="V29" t="n">
         <v>1.21</v>
@@ -5088,7 +5088,7 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AK29" t="n">
         <v>1.64</v>
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,65 +5177,65 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.37</v>
+        <v>1.99</v>
       </c>
       <c r="O30" t="n">
-        <v>3.06</v>
+        <v>2.93</v>
       </c>
       <c r="P30" t="n">
-        <v>2.92</v>
+        <v>4.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="R30" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="S30" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="T30" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="U30" t="n">
-        <v>3.3</v>
+        <v>3.98</v>
       </c>
       <c r="V30" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y30" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB30" t="n">
+      <c r="AF30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG30" t="n">
         <v>1.5</v>
       </c>
-      <c r="AC30" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AH30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O31" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="P31" t="n">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.8</v>
+        <v>2.57</v>
       </c>
       <c r="R31" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="S31" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="T31" t="n">
-        <v>2.28</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>3.98</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.19</v>
+        <v>2.83</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.8</v>
+        <v>3.99</v>
       </c>
       <c r="AD31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.07</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF31" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,34 +5495,34 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="O32" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U32" t="n">
         <v>3.3</v>
       </c>
-      <c r="P32" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U32" t="n">
-        <v>3</v>
-      </c>
       <c r="V32" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
         <v>1.03</v>
@@ -5531,28 +5531,28 @@
         <v>1.37</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>1.33</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5672,7 +5672,7 @@
         <v>1.62</v>
       </c>
       <c r="T33" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="U33" t="n">
         <v>3.95</v>
@@ -5684,7 +5684,7 @@
         <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="Y33" t="n">
         <v>1.57</v>
@@ -5693,16 +5693,16 @@
         <v>2.25</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.74</v>
+        <v>2.87</v>
       </c>
       <c r="AB33" t="n">
         <v>1.39</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.85</v>
+        <v>5.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AE33" t="n">
         <v>1.03</v>
@@ -5727,7 +5727,7 @@
         <v>1.32</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,13 +5972,13 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -6011,10 +6011,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.89</v>
+        <v>2.19</v>
       </c>
       <c r="O36" t="n">
-        <v>3.45</v>
+        <v>2.7</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB36" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O37" t="n">
-        <v>3.38</v>
+        <v>3.45</v>
       </c>
       <c r="P37" t="n">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="Q37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R37" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T37" t="n">
         <v>2.56</v>
       </c>
-      <c r="R37" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T37" t="n">
-        <v>2.53</v>
-      </c>
       <c r="U37" t="n">
-        <v>3.11</v>
+        <v>2.77</v>
       </c>
       <c r="V37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y37" t="n">
         <v>1.33</v>
       </c>
-      <c r="W37" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.35</v>
-      </c>
       <c r="Z37" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK37" t="n">
         <v>1.83</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O38" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P38" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.72</v>
+        <v>2.14</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6770,61 +6770,61 @@
         <v>2.3</v>
       </c>
       <c r="O40" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="P40" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6935,19 +6935,19 @@
         <v>4.81</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="R41" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="S41" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="T41" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="U41" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="V41" t="n">
         <v>1.16</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.6</v>
+        <v>2.25</v>
       </c>
       <c r="O42" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="P42" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="O44" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="P44" t="n">
-        <v>3.2</v>
+        <v>13</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.04</v>
+        <v>1.53</v>
       </c>
       <c r="R44" t="n">
-        <v>1.89</v>
+        <v>3.3</v>
       </c>
       <c r="S44" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="T44" t="n">
-        <v>2.36</v>
+        <v>5.5</v>
       </c>
       <c r="U44" t="n">
-        <v>3.35</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>1.27</v>
+        <v>2.15</v>
       </c>
       <c r="W44" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="X44" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.56</v>
+        <v>7.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.5</v>
+        <v>1.21</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.19</v>
+        <v>2.19</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.31</v>
+        <v>1.05</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.57</v>
+        <v>4.1</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.99</v>
+        <v>2.35</v>
       </c>
       <c r="O45" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="P45" t="n">
-        <v>4.31</v>
+        <v>3.36</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>1.36</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.17</v>
+        <v>2.6</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>2.85</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>2.3</v>
+        <v>1.99</v>
       </c>
       <c r="O47" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="P47" t="n">
-        <v>3.1</v>
+        <v>4.31</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
@@ -7919,10 +7919,10 @@
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.36</v>
+        <v>1.66</v>
       </c>
       <c r="AC47" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -749,7 +749,7 @@
         <v>2.5</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
         <v>1.07</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="T8" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="U8" t="n">
-        <v>2.03</v>
+        <v>2.39</v>
       </c>
       <c r="V8" t="n">
-        <v>1.73</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>6.5</v>
+        <v>4.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.16</v>
+        <v>2.23</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.96</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.99</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="S9" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
-        <v>3.3</v>
+        <v>3.84</v>
       </c>
       <c r="U9" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="W9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
         <v>1.08</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.2</v>
-      </c>
       <c r="Z9" t="n">
-        <v>4.39</v>
+        <v>5.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.23</v>
+        <v>3.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,10 +1997,10 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3.86</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
         <v>2.42</v>
@@ -2024,25 +2024,25 @@
         <v>1.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z10" t="n">
         <v>9.65</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
         <v>1.8</v>
@@ -2051,7 +2051,7 @@
         <v>1.34</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AG10" t="n">
         <v>2.8</v>
@@ -2070,7 +2070,7 @@
         <v>1.26</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2633,40 +2633,40 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="R14" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="S14" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T14" t="n">
         <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z14" t="n">
         <v>2.8</v>
@@ -2690,7 +2690,7 @@
         <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.64</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.57</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>2.32</v>
+        <v>2.74</v>
       </c>
       <c r="S15" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T15" t="n">
-        <v>3.18</v>
+        <v>3.92</v>
       </c>
       <c r="U15" t="n">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="W15" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.54</v>
+        <v>2.03</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.08</v>
+        <v>3.05</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>3.63</v>
+        <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.6</v>
+        <v>4.34</v>
       </c>
       <c r="R16" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="S16" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>2.73</v>
+        <v>2.21</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK16" t="n">
         <v>1.08</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,23 +3265,23 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3290,13 +3290,13 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -3308,25 +3308,25 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.96</v>
       </c>
       <c r="P19" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T19" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
         <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
         <v>1.97</v>
@@ -3587,31 +3587,31 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="O20" t="n">
         <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.43</v>
+        <v>2.21</v>
       </c>
       <c r="S20" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T20" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
@@ -3620,31 +3620,31 @@
         <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
         <v>4.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,64 +3746,64 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="O21" t="n">
-        <v>8.65</v>
+        <v>7.5</v>
       </c>
       <c r="P21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="R21" t="n">
-        <v>3.3</v>
+        <v>3.19</v>
       </c>
       <c r="S21" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="T21" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V21" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Z21" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AB21" t="n">
         <v>3.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AK21" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O22" t="n">
         <v>2.62</v>
@@ -3917,7 +3917,7 @@
         <v>3.48</v>
       </c>
       <c r="R22" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="S22" t="n">
         <v>1.67</v>
@@ -3926,10 +3926,10 @@
         <v>2.07</v>
       </c>
       <c r="U22" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="V22" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
         <v>1.03</v>
@@ -3944,7 +3944,7 @@
         <v>2.19</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AB22" t="n">
         <v>1.36</v>
@@ -3975,7 +3975,7 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK22" t="n">
         <v>1.4</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,64 +4541,64 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="O26" t="n">
-        <v>4.95</v>
+        <v>6.7</v>
       </c>
       <c r="P26" t="n">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="R26" t="n">
-        <v>2.57</v>
+        <v>3.04</v>
       </c>
       <c r="S26" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T26" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V26" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD26" t="n">
         <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.75</v>
+        <v>2.49</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,31 +4700,31 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="O27" t="n">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="P27" t="n">
-        <v>13</v>
+        <v>6.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="R27" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="S27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U27" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W27" t="n">
         <v>1.14</v>
@@ -4733,31 +4733,31 @@
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.65</v>
+        <v>4.88</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AD27" t="n">
         <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.63</v>
+        <v>1.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AK27" t="n">
-        <v>5</v>
+        <v>2.82</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4865,58 +4865,58 @@
         <v>4.05</v>
       </c>
       <c r="P28" t="n">
-        <v>4.89</v>
+        <v>4.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="S28" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="T28" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="U28" t="n">
         <v>2.69</v>
       </c>
       <c r="V28" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
         <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5018,13 +5018,13 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O29" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="P29" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="Q29" t="n">
         <v>2.88</v>
@@ -5039,7 +5039,7 @@
         <v>2.38</v>
       </c>
       <c r="U29" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="V29" t="n">
         <v>1.21</v>
@@ -5057,7 +5057,7 @@
         <v>2.32</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AB29" t="n">
         <v>1.4</v>
@@ -5186,7 +5186,7 @@
         <v>4.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="R30" t="n">
         <v>1.77</v>
@@ -5195,37 +5195,37 @@
         <v>1.57</v>
       </c>
       <c r="T30" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="U30" t="n">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="V30" t="n">
         <v>1.18</v>
       </c>
       <c r="W30" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X30" t="n">
         <v>1.09</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="AC30" t="n">
         <v>5.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AE30" t="n">
         <v>1.03</v>
@@ -5234,7 +5234,7 @@
         <v>2.4</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,34 +5336,34 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="O31" t="n">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="P31" t="n">
-        <v>4.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.57</v>
+        <v>3.16</v>
       </c>
       <c r="R31" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="S31" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
         <v>1.03</v>
@@ -5372,28 +5372,28 @@
         <v>1.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>1.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,34 +5495,34 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="O32" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="P32" t="n">
-        <v>2.92</v>
+        <v>4.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.16</v>
+        <v>2.57</v>
       </c>
       <c r="R32" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="S32" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="T32" t="n">
-        <v>2.47</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
         <v>1.03</v>
@@ -5531,28 +5531,28 @@
         <v>1.37</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>1.33</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,65 +5654,65 @@
         </is>
       </c>
       <c r="N33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O33" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="P33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG33" t="n">
         <v>2.05</v>
       </c>
-      <c r="O33" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AH33" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.63</v>
+        <v>2.62</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,80 +5813,80 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="O34" t="n">
-        <v>4.8</v>
+        <v>2.84</v>
       </c>
       <c r="P34" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.85</v>
+        <v>2.88</v>
       </c>
       <c r="R34" t="n">
-        <v>2.5</v>
+        <v>1.78</v>
       </c>
       <c r="S34" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="U34" t="n">
-        <v>2.31</v>
+        <v>3.95</v>
       </c>
       <c r="V34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.57</v>
       </c>
-      <c r="W34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.18</v>
-      </c>
       <c r="Z34" t="n">
-        <v>4.75</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK34" t="n">
         <v>1.63</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>2.79</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.42</v>
+        <v>2.11</v>
       </c>
       <c r="O35" t="n">
-        <v>3.22</v>
+        <v>3.38</v>
       </c>
       <c r="P35" t="n">
-        <v>2.57</v>
+        <v>3.68</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.07</v>
+        <v>1.68</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="O36" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="P36" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="O37" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P37" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Midland</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="O38" t="n">
-        <v>3.38</v>
+        <v>2.76</v>
       </c>
       <c r="P38" t="n">
-        <v>3.68</v>
+        <v>3.87</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB38" t="n">
         <v>1.33</v>
       </c>
-      <c r="W38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AC38" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.3</v>
+        <v>1.89</v>
       </c>
       <c r="O40" t="n">
-        <v>2.43</v>
+        <v>3.45</v>
       </c>
       <c r="P40" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.3</v>
+        <v>2.39</v>
       </c>
       <c r="R40" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="S40" t="n">
-        <v>1.79</v>
+        <v>1.43</v>
       </c>
       <c r="T40" t="n">
-        <v>1.99</v>
+        <v>2.55</v>
       </c>
       <c r="U40" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="V40" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="W40" t="n">
         <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.81</v>
+        <v>1.34</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.1</v>
+        <v>2.12</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.5</v>
+        <v>3.68</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.54</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.48</v>
+        <v>1.89</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6962,10 +6962,10 @@
         <v>1.65</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.92</v>
+        <v>3.4</v>
       </c>
       <c r="AB41" t="n">
         <v>1.33</v>
@@ -7091,58 +7091,58 @@
         <v>2.9</v>
       </c>
       <c r="P42" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="R42" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="S42" t="n">
         <v>1.45</v>
       </c>
       <c r="T42" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="U42" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="V42" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
         <v>1.07</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.5</v>
+        <v>4.59</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="O43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
         <v>3.1</v>
       </c>
-      <c r="P43" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="R43" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U43" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W43" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AB43" t="n">
-        <v>1.97</v>
+        <v>1.36</v>
       </c>
       <c r="AC43" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.17</v>
+        <v>3.13</v>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>2.79</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>2.55</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="O45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P45" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R45" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z45" t="n">
         <v>2.75</v>
       </c>
-      <c r="P45" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>0</v>
-      </c>
       <c r="AA45" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.6</v>
+        <v>1.17</v>
       </c>
       <c r="O46" t="n">
-        <v>2.95</v>
+        <v>6</v>
       </c>
       <c r="P46" t="n">
-        <v>2.85</v>
+        <v>13</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -8039,34 +8039,34 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="O48" t="n">
-        <v>4.45</v>
+        <v>4.73</v>
       </c>
       <c r="P48" t="n">
-        <v>6</v>
+        <v>7.02</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="R48" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S48" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T48" t="n">
         <v>3.22</v>
       </c>
       <c r="U48" t="n">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V48" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W48" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X48" t="n">
         <v>1.04</v>
@@ -8075,13 +8075,13 @@
         <v>1.22</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC48" t="n">
         <v>2.8</v>
@@ -8093,7 +8093,7 @@
         <v>1.15</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG48" t="n">
         <v>1.91</v>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AK48" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -8198,64 +8198,64 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2.51</v>
+        <v>2.79</v>
       </c>
       <c r="O49" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P49" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q49" t="n">
         <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="S49" t="n">
         <v>1.25</v>
       </c>
       <c r="T49" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="U49" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V49" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W49" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X49" t="n">
         <v>1.03</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z49" t="n">
         <v>4.6</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AC49" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AD49" t="n">
         <v>1.52</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG49" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="AJ49" t="n">
-        <v>1.52</v>
+        <v>1.24</v>
       </c>
       <c r="AK49" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU49"/>
+  <dimension ref="A1:AU48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1052,55 +1052,55 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.5</v>
+        <v>1.74</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="P11" t="n">
-        <v>6.36</v>
+        <v>4.61</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>1.5</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>6.36</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>4.61</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>3.63</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="P15" t="n">
-        <v>7.5</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>5.82</v>
       </c>
       <c r="R15" t="n">
-        <v>2.74</v>
+        <v>2.12</v>
       </c>
       <c r="S15" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>2.65</v>
       </c>
       <c r="V15" t="n">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>3.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.03</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.05</v>
+        <v>1.15</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.64</v>
+        <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5</v>
+        <v>7.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.34</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>2.45</v>
+        <v>2.74</v>
       </c>
       <c r="S16" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>3.18</v>
+        <v>3.92</v>
       </c>
       <c r="U16" t="n">
-        <v>2.21</v>
+        <v>1.86</v>
       </c>
       <c r="V16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.57</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.08</v>
+        <v>3.05</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,80 +3110,80 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.63</v>
+        <v>5.25</v>
       </c>
       <c r="O17" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.82</v>
+        <v>4.34</v>
       </c>
       <c r="R17" t="n">
-        <v>2.12</v>
+        <v>2.29</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="U17" t="n">
-        <v>2.65</v>
+        <v>2.21</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="W17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3944,13 +3944,13 @@
         <v>2.19</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="AD22" t="n">
         <v>1.08</v>
@@ -3962,7 +3962,7 @@
         <v>2.23</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,34 +4541,34 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="O26" t="n">
-        <v>6.7</v>
+        <v>4.95</v>
       </c>
       <c r="P26" t="n">
-        <v>19.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>3.04</v>
+        <v>2.57</v>
       </c>
       <c r="S26" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="T26" t="n">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="U26" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
@@ -4577,28 +4577,28 @@
         <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.65</v>
+        <v>4.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AD26" t="n">
         <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.49</v>
+        <v>1.76</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK26" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,34 +4700,34 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="O27" t="n">
-        <v>4.8</v>
+        <v>6.7</v>
       </c>
       <c r="P27" t="n">
-        <v>6.9</v>
+        <v>19.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="R27" t="n">
-        <v>2.47</v>
+        <v>3.04</v>
       </c>
       <c r="S27" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="T27" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V27" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
@@ -4736,28 +4736,28 @@
         <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.88</v>
+        <v>4.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AD27" t="n">
         <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.78</v>
+        <v>2.49</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.94</v>
+        <v>1.48</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.82</v>
+        <v>5</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Racing Córdoba</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -5018,64 +5018,64 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2</v>
+        <v>2.37</v>
       </c>
       <c r="O29" t="n">
-        <v>2.9</v>
+        <v>2.61</v>
       </c>
       <c r="P29" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5088,10 +5088,10 @@
         </is>
       </c>
       <c r="AJ29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -5121,7 +5121,7 @@
         <v>0</v>
       </c>
       <c r="AU29" s="3" t="n">
-        <v>46220.75</v>
+        <v>46220.66666666666</v>
       </c>
     </row>
     <row r="30">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -5177,64 +5177,64 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O30" t="n">
-        <v>2.93</v>
+        <v>2.87</v>
       </c>
       <c r="P30" t="n">
-        <v>4.35</v>
+        <v>3.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="R30" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="S30" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="T30" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U30" t="n">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="V30" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W30" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X30" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.8</v>
+        <v>5.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         <v>0</v>
       </c>
       <c r="AU30" s="3" t="n">
-        <v>46220.79166666666</v>
+        <v>46220.75</v>
       </c>
     </row>
     <row r="31">
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,34 +5336,34 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.37</v>
+        <v>1.91</v>
       </c>
       <c r="O31" t="n">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="P31" t="n">
-        <v>2.9</v>
+        <v>4.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.16</v>
+        <v>2.57</v>
       </c>
       <c r="R31" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="S31" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="T31" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U31" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
         <v>1.03</v>
@@ -5372,28 +5372,28 @@
         <v>1.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.66</v>
+        <v>2.83</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.1</v>
+        <v>3.99</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>1.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="O32" t="n">
-        <v>3.3</v>
+        <v>2.93</v>
       </c>
       <c r="P32" t="n">
-        <v>4.05</v>
+        <v>4.35</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.57</v>
+        <v>3.02</v>
       </c>
       <c r="R32" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="S32" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="U32" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="V32" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.44</v>
+        <v>2.37</v>
       </c>
       <c r="O33" t="n">
-        <v>4.78</v>
+        <v>3.06</v>
       </c>
       <c r="P33" t="n">
-        <v>6.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.96</v>
+        <v>3.16</v>
       </c>
       <c r="R33" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="U33" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA33" t="n">
         <v>2.32</v>
       </c>
-      <c r="S33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AB33" t="n">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.45</v>
+        <v>4.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.51</v>
+        <v>1.16</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.2</v>
+        <v>1.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="3" t="n">
-        <v>46220.8125</v>
+        <v>46220.79166666666</v>
       </c>
     </row>
     <row r="34">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,65 +5813,65 @@
         </is>
       </c>
       <c r="N34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O34" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="P34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2.05</v>
       </c>
-      <c r="O34" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U34" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.63</v>
+        <v>2.62</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5925,12 +5925,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O35" t="n">
-        <v>3.38</v>
+        <v>2.84</v>
       </c>
       <c r="P35" t="n">
-        <v>3.68</v>
+        <v>3.85</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="R35" t="n">
-        <v>2.02</v>
+        <v>1.78</v>
       </c>
       <c r="S35" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="T35" t="n">
-        <v>2.65</v>
+        <v>2.16</v>
       </c>
       <c r="U35" t="n">
-        <v>3.02</v>
+        <v>3.95</v>
       </c>
       <c r="V35" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="W35" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.36</v>
+        <v>1.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.15</v>
+        <v>2.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.68</v>
+        <v>1.39</v>
       </c>
       <c r="AC35" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.21</v>
+        <v>1.07</v>
       </c>
       <c r="AE35" t="n">
         <v>1.03</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.83</v>
+        <v>1.54</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6075,7 +6075,7 @@
         <v>0</v>
       </c>
       <c r="AU35" s="3" t="n">
-        <v>46220.83333333334</v>
+        <v>46220.8125</v>
       </c>
     </row>
     <row r="36">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.25</v>
+        <v>2.42</v>
       </c>
       <c r="O36" t="n">
-        <v>2.45</v>
+        <v>3.22</v>
       </c>
       <c r="P36" t="n">
-        <v>3.6</v>
+        <v>2.57</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.2</v>
+        <v>1.72</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="AC36" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.42</v>
+        <v>2.18</v>
       </c>
       <c r="O37" t="n">
-        <v>3.22</v>
+        <v>2.45</v>
       </c>
       <c r="P37" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF37" t="n">
         <v>2.57</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Midland</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="O38" t="n">
-        <v>2.76</v>
+        <v>3.38</v>
       </c>
       <c r="P38" t="n">
-        <v>3.87</v>
+        <v>3.68</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6935,10 +6935,10 @@
         <v>4.81</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="R41" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="S41" t="n">
         <v>1.67</v>
@@ -6956,34 +6956,34 @@
         <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y41" t="n">
         <v>1.65</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AA41" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.15</v>
+        <v>6.43</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AE41" t="n">
         <v>1.02</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Racing Córdoba</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="O43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P43" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z43" t="n">
         <v>2.75</v>
       </c>
-      <c r="P43" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
       <c r="AA43" t="n">
-        <v>3.1</v>
+        <v>1.83</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,13 +7403,13 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>3.13</v>
+        <v>1.99</v>
       </c>
       <c r="O44" t="n">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="P44" t="n">
-        <v>2.55</v>
+        <v>4.31</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -7442,10 +7442,10 @@
         <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.87</v>
+        <v>3.13</v>
       </c>
       <c r="O45" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="P45" t="n">
-        <v>4.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlanta United FC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7880,64 +7880,64 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.99</v>
+        <v>1.44</v>
       </c>
       <c r="O47" t="n">
-        <v>2.95</v>
+        <v>4.62</v>
       </c>
       <c r="P47" t="n">
-        <v>4.31</v>
+        <v>6.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.05</v>
+        <v>1.69</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -7950,10 +7950,10 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="AU47" s="3" t="n">
-        <v>46220.875</v>
+        <v>46220.88194444445</v>
       </c>
     </row>
     <row r="48">
@@ -7992,7 +7992,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>23:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>LA Galaxy</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Atlanta United FC</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -8039,81 +8039,81 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>1.47</v>
+        <v>2.6</v>
       </c>
       <c r="O48" t="n">
-        <v>4.73</v>
+        <v>3.5</v>
       </c>
       <c r="P48" t="n">
-        <v>7.02</v>
+        <v>2.22</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.91</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
         <v>2.3</v>
       </c>
       <c r="S48" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T48" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U48" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="V48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W48" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X48" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD48" t="n">
         <v>1.52</v>
       </c>
-      <c r="W48" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X48" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD48" t="n">
+      <c r="AE48" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK48" t="n">
         <v>1.4</v>
       </c>
-      <c r="AE48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>2.71</v>
-      </c>
       <c r="AL48" t="n">
         <v>0</v>
       </c>
@@ -8142,165 +8142,6 @@
         <v>0</v>
       </c>
       <c r="AU48" s="3" t="n">
-        <v>46220.88194444445</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="n">
-        <v>46220</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>23:25</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>USA MLS</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>LA Galaxy</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Los Angeles FC</t>
-        </is>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="O49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R49" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="S49" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T49" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="U49" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W49" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X49" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AG49" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ49" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK49" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AL49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP49" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU49" s="3" t="n">
         <v>46220.97569444445</v>
       </c>
     </row>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,13 +1361,13 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>6.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T8" t="n">
-        <v>3.25</v>
+        <v>3.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.39</v>
+        <v>2.04</v>
       </c>
       <c r="V8" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="W8" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
         <v>1.08</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Z8" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.23</v>
+        <v>3.16</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.2</v>
+        <v>2.49</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>6.92</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="T9" t="n">
-        <v>3.84</v>
+        <v>3.25</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.39</v>
       </c>
       <c r="V9" t="n">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.16</v>
+        <v>2.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.58</v>
+        <v>1.71</v>
       </c>
       <c r="AG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AK9" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.49</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.74</v>
+        <v>1.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="P11" t="n">
-        <v>4.61</v>
+        <v>6.36</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P12" t="n">
-        <v>6.36</v>
+        <v>1.91</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>4.61</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.63</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>3.28</v>
+        <v>5.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>7.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.82</v>
+        <v>1.73</v>
       </c>
       <c r="R15" t="n">
-        <v>2.12</v>
+        <v>2.74</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>3.92</v>
       </c>
       <c r="U15" t="n">
-        <v>2.65</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA15" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.14</v>
+        <v>1.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>2.03</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.88</v>
+        <v>2.23</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>2.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.15</v>
+        <v>3.05</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.25</v>
+        <v>3.63</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.34</v>
+        <v>5.82</v>
       </c>
       <c r="R17" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="S17" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T17" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.21</v>
+        <v>2.65</v>
       </c>
       <c r="V17" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.52</v>
+        <v>1.92</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.24</v>
+        <v>1.85</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.34</v>
+        <v>3.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,43 +3428,43 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S19" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U19" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA19" t="n">
         <v>1.66</v>
@@ -3473,19 +3473,19 @@
         <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,43 +3587,43 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="P20" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="R20" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U20" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AA20" t="n">
         <v>1.66</v>
@@ -3632,19 +3632,19 @@
         <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,34 +4541,34 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="O26" t="n">
-        <v>4.95</v>
+        <v>6.7</v>
       </c>
       <c r="P26" t="n">
-        <v>7.75</v>
+        <v>19.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="R26" t="n">
-        <v>2.57</v>
+        <v>3.04</v>
       </c>
       <c r="S26" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="T26" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V26" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
@@ -4577,28 +4577,28 @@
         <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.88</v>
+        <v>4.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AD26" t="n">
         <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.76</v>
+        <v>2.49</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,34 +4700,34 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="O27" t="n">
-        <v>6.7</v>
+        <v>4.95</v>
       </c>
       <c r="P27" t="n">
-        <v>19.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="R27" t="n">
-        <v>3.04</v>
+        <v>2.57</v>
       </c>
       <c r="S27" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="T27" t="n">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="U27" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
@@ -4736,28 +4736,28 @@
         <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.65</v>
+        <v>4.88</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AD27" t="n">
         <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.49</v>
+        <v>1.76</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK27" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,34 +5336,34 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.91</v>
+        <v>2.37</v>
       </c>
       <c r="O31" t="n">
-        <v>3.3</v>
+        <v>3.06</v>
       </c>
       <c r="P31" t="n">
-        <v>4.05</v>
+        <v>2.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.57</v>
+        <v>3.16</v>
       </c>
       <c r="R31" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="S31" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="U31" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
         <v>1.03</v>
@@ -5372,28 +5372,28 @@
         <v>1.37</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.83</v>
+        <v>2.66</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>1.33</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="O32" t="n">
-        <v>2.93</v>
+        <v>3.3</v>
       </c>
       <c r="P32" t="n">
-        <v>4.35</v>
+        <v>4.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.02</v>
+        <v>2.57</v>
       </c>
       <c r="R32" t="n">
-        <v>1.77</v>
+        <v>1.98</v>
       </c>
       <c r="S32" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="T32" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U32" t="n">
+        <v>3</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA32" t="n">
         <v>2.2</v>
       </c>
-      <c r="U32" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.63</v>
-      </c>
       <c r="AB32" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AC32" t="n">
-        <v>5.8</v>
+        <v>3.99</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.37</v>
+        <v>1.99</v>
       </c>
       <c r="O33" t="n">
-        <v>3.06</v>
+        <v>2.93</v>
       </c>
       <c r="P33" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="R33" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="S33" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="T33" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="U33" t="n">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="V33" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE33" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF33" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="O34" t="n">
-        <v>4.78</v>
+        <v>2.84</v>
       </c>
       <c r="P34" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="R34" t="n">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="S34" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="U34" t="n">
-        <v>2.31</v>
+        <v>3.95</v>
       </c>
       <c r="V34" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="W34" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>4.65</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.45</v>
+        <v>5.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.51</v>
+        <v>1.07</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,65 +5972,65 @@
         </is>
       </c>
       <c r="N35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O35" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="P35" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R35" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG35" t="n">
         <v>2.05</v>
       </c>
-      <c r="O35" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P35" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U35" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AH35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.42</v>
+        <v>1.89</v>
       </c>
       <c r="O36" t="n">
-        <v>3.22</v>
+        <v>3.45</v>
       </c>
       <c r="P36" t="n">
-        <v>2.57</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.72</v>
+        <v>2.12</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.07</v>
+        <v>1.78</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="O37" t="n">
-        <v>2.45</v>
+        <v>3.38</v>
       </c>
       <c r="P37" t="n">
-        <v>4.26</v>
+        <v>3.68</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.12</v>
+        <v>2.56</v>
       </c>
       <c r="R37" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="S37" t="n">
-        <v>1.62</v>
+        <v>1.42</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="U37" t="n">
-        <v>4.4</v>
+        <v>3.02</v>
       </c>
       <c r="V37" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.28</v>
+        <v>1.68</v>
       </c>
       <c r="AC37" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.55</v>
+        <v>1.78</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="O38" t="n">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="P38" t="n">
-        <v>3.68</v>
+        <v>4.26</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.56</v>
+        <v>3.12</v>
       </c>
       <c r="R38" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="S38" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="T38" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>3.02</v>
+        <v>4.4</v>
       </c>
       <c r="V38" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="W38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD38" t="n">
         <v>1.05</v>
       </c>
-      <c r="X38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE38" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.91</v>
+        <v>2.57</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.89</v>
+        <v>2.42</v>
       </c>
       <c r="O40" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>2.57</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.87</v>
+        <v>3.13</v>
       </c>
       <c r="O43" t="n">
-        <v>3.1</v>
+        <v>2.79</v>
       </c>
       <c r="P43" t="n">
-        <v>4.26</v>
+        <v>2.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="O44" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P44" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,13 +7562,13 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>3.13</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
-        <v>2.79</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
-        <v>2.55</v>
+        <v>4.31</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -7601,10 +7601,10 @@
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC45" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -893,19 +893,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.6</v>
+        <v>3.66</v>
       </c>
       <c r="R3" t="n">
-        <v>2.23</v>
+        <v>2.46</v>
       </c>
       <c r="S3" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
         <v>1.52</v>
@@ -917,31 +917,31 @@
         <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AA3" t="n">
         <v>1.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC3" t="n">
         <v>2.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AE3" t="n">
         <v>1.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1679,31 +1679,31 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
-        <v>5.36</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>6.92</v>
+        <v>5.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R8" t="n">
         <v>2.52</v>
       </c>
       <c r="S8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T8" t="n">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="U8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="V8" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="W8" t="n">
         <v>1.17</v>
@@ -1730,7 +1730,7 @@
         <v>1.79</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AF8" t="n">
         <v>1.58</v>
@@ -1749,7 +1749,7 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AK8" t="n">
         <v>2.49</v>
@@ -1838,25 +1838,25 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="R9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T9" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="U9" t="n">
         <v>2.39</v>
@@ -1865,22 +1865,22 @@
         <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
         <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.4</v>
+        <v>4.35</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AC9" t="n">
         <v>2.66</v>
@@ -1889,10 +1889,10 @@
         <v>1.47</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG9" t="n">
         <v>2</v>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,13 +1997,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="P10" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q10" t="n">
         <v>2.99</v>
@@ -2012,10 +2012,10 @@
         <v>2.42</v>
       </c>
       <c r="S10" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="T10" t="n">
-        <v>3.86</v>
+        <v>4.8</v>
       </c>
       <c r="U10" t="n">
         <v>1.99</v>
@@ -2033,44 +2033,44 @@
         <v>1.08</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.65</v>
+        <v>6.18</v>
       </c>
       <c r="AA10" t="n">
         <v>1.38</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.7</v>
+        <v>3.22</v>
       </c>
       <c r="AC10" t="n">
         <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AF10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.37</v>
       </c>
-      <c r="AG10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.9</v>
+        <v>1.74</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="P12" t="n">
-        <v>1.91</v>
+        <v>4.61</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.74</v>
+        <v>3.9</v>
       </c>
       <c r="O13" t="n">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>4.61</v>
+        <v>1.91</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>3.63</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>3.28</v>
       </c>
       <c r="P15" t="n">
-        <v>7.5</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.73</v>
+        <v>5.82</v>
       </c>
       <c r="R15" t="n">
-        <v>2.74</v>
+        <v>2.12</v>
       </c>
       <c r="S15" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="T15" t="n">
-        <v>3.92</v>
+        <v>2.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>2.65</v>
       </c>
       <c r="V15" t="n">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>3.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.03</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.23</v>
+        <v>1.88</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.04</v>
+        <v>2.07</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.05</v>
+        <v>1.15</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>3.63</v>
+        <v>1.28</v>
       </c>
       <c r="O17" t="n">
-        <v>3.28</v>
+        <v>5.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.03</v>
+        <v>7.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.82</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>2.12</v>
+        <v>2.74</v>
       </c>
       <c r="S17" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8</v>
+        <v>3.92</v>
       </c>
       <c r="U17" t="n">
-        <v>2.65</v>
+        <v>1.86</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.14</v>
+        <v>1.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.3</v>
+        <v>2.03</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.07</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.88</v>
+        <v>2.23</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>2.07</v>
+        <v>1.04</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.15</v>
+        <v>3.05</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,43 +3428,43 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="P19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="R19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="U19" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="V19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AA19" t="n">
         <v>1.66</v>
@@ -3473,19 +3473,19 @@
         <v>2.15</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,43 +3587,43 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3.96</v>
+        <v>3.7</v>
       </c>
       <c r="P20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="S20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
         <v>1.66</v>
@@ -3632,19 +3632,19 @@
         <v>2.15</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,34 +4541,34 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="O26" t="n">
-        <v>6.7</v>
+        <v>4.95</v>
       </c>
       <c r="P26" t="n">
-        <v>19.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="R26" t="n">
-        <v>3.04</v>
+        <v>2.57</v>
       </c>
       <c r="S26" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="T26" t="n">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="U26" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W26" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
@@ -4577,28 +4577,28 @@
         <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.65</v>
+        <v>4.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="AD26" t="n">
         <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.49</v>
+        <v>1.76</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.48</v>
+        <v>1.93</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AK26" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,34 +4700,34 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="O27" t="n">
-        <v>4.95</v>
+        <v>6.7</v>
       </c>
       <c r="P27" t="n">
-        <v>7.75</v>
+        <v>19.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="R27" t="n">
-        <v>2.57</v>
+        <v>3.04</v>
       </c>
       <c r="S27" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="T27" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="V27" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
@@ -4736,28 +4736,28 @@
         <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.88</v>
+        <v>4.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AD27" t="n">
         <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.76</v>
+        <v>2.49</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AK27" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.37</v>
+        <v>1.99</v>
       </c>
       <c r="O31" t="n">
-        <v>3.06</v>
+        <v>2.93</v>
       </c>
       <c r="P31" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.16</v>
+        <v>3.02</v>
       </c>
       <c r="R31" t="n">
-        <v>2.06</v>
+        <v>1.77</v>
       </c>
       <c r="S31" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="T31" t="n">
-        <v>2.59</v>
+        <v>2.2</v>
       </c>
       <c r="U31" t="n">
-        <v>3.22</v>
+        <v>3.75</v>
       </c>
       <c r="V31" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AF31" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.78</v>
+        <v>1.53</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.99</v>
+        <v>2.37</v>
       </c>
       <c r="O33" t="n">
-        <v>2.93</v>
+        <v>3.06</v>
       </c>
       <c r="P33" t="n">
-        <v>4.35</v>
+        <v>2.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.02</v>
+        <v>3.16</v>
       </c>
       <c r="R33" t="n">
-        <v>1.77</v>
+        <v>2.06</v>
       </c>
       <c r="S33" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="T33" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="U33" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="V33" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="W33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X33" t="n">
         <v>1.03</v>
       </c>
-      <c r="X33" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Y33" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.45</v>
+        <v>2.66</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.63</v>
+        <v>2.32</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,65 +5813,65 @@
         </is>
       </c>
       <c r="N34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O34" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="P34" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R34" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AG34" t="n">
         <v>2.05</v>
       </c>
-      <c r="O34" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P34" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S34" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U34" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AH34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="O35" t="n">
-        <v>4.78</v>
+        <v>2.84</v>
       </c>
       <c r="P35" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.96</v>
+        <v>2.8</v>
       </c>
       <c r="R35" t="n">
-        <v>2.32</v>
+        <v>1.78</v>
       </c>
       <c r="S35" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="T35" t="n">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="U35" t="n">
-        <v>2.31</v>
+        <v>3.95</v>
       </c>
       <c r="V35" t="n">
-        <v>1.57</v>
+        <v>1.17</v>
       </c>
       <c r="W35" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.12</v>
+        <v>1.6</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.65</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.45</v>
+        <v>5.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.51</v>
+        <v>1.07</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.05</v>
+        <v>1.54</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.62</v>
+        <v>1.62</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="O37" t="n">
-        <v>3.38</v>
+        <v>2.45</v>
       </c>
       <c r="P37" t="n">
-        <v>3.68</v>
+        <v>4.26</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.56</v>
+        <v>3.12</v>
       </c>
       <c r="R37" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="S37" t="n">
-        <v>1.42</v>
+        <v>1.62</v>
       </c>
       <c r="T37" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="U37" t="n">
-        <v>3.02</v>
+        <v>4.4</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="W37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD37" t="n">
         <v>1.05</v>
       </c>
-      <c r="X37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AE37" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>2.57</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="O38" t="n">
-        <v>2.45</v>
+        <v>3.45</v>
       </c>
       <c r="P38" t="n">
-        <v>4.26</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.12</v>
+        <v>2.39</v>
       </c>
       <c r="R38" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="S38" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="T38" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="U38" t="n">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="V38" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="W38" t="n">
         <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="AC38" t="n">
-        <v>6.5</v>
+        <v>3.68</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.25</v>
+        <v>3.13</v>
       </c>
       <c r="O42" t="n">
-        <v>2.9</v>
+        <v>2.79</v>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.59</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>3.13</v>
+        <v>2.25</v>
       </c>
       <c r="O43" t="n">
-        <v>2.79</v>
+        <v>2.9</v>
       </c>
       <c r="P43" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>4.59</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.87</v>
+        <v>1.17</v>
       </c>
       <c r="O44" t="n">
-        <v>3.1</v>
+        <v>6</v>
       </c>
       <c r="P44" t="n">
-        <v>4.26</v>
+        <v>13</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="R44" t="n">
-        <v>2.13</v>
+        <v>3.3</v>
       </c>
       <c r="S44" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="T44" t="n">
-        <v>2.88</v>
+        <v>5.5</v>
       </c>
       <c r="U44" t="n">
-        <v>2.66</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="W44" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.24</v>
+        <v>1.03</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.75</v>
+        <v>7.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.83</v>
+        <v>1.21</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.75</v>
+        <v>1.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.3</v>
+        <v>2.19</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.06</v>
+        <v>1.51</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.83</v>
+        <v>2.19</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="O45" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P45" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>1.91</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.17</v>
+        <v>1.99</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>4.31</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -725,61 +725,61 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.23</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.79</v>
+        <v>3.24</v>
       </c>
       <c r="R2" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="S2" t="n">
         <v>1.3</v>
       </c>
       <c r="T2" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AB2" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
         <v>1.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG2" t="n">
         <v>2.2</v>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.52</v>
+        <v>1.38</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -920,13 +920,13 @@
         <v>1.21</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="AA3" t="n">
         <v>1.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AC3" t="n">
         <v>2.7</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.45</v>
+        <v>3.92</v>
       </c>
       <c r="O4" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3.46</v>
       </c>
       <c r="O6" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="P6" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="O8" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="P8" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK8" t="n">
         <v>2.52</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2.49</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.54</v>
+        <v>1.39</v>
       </c>
       <c r="O9" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="T9" t="n">
-        <v>3.22</v>
+        <v>4.5</v>
       </c>
       <c r="U9" t="n">
-        <v>2.39</v>
+        <v>2.03</v>
       </c>
       <c r="V9" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.35</v>
+        <v>5.7</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.21</v>
+        <v>3.16</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.66</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
         <v>3.85</v>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AK10" t="n">
         <v>1.35</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.5</v>
+        <v>3.78</v>
       </c>
       <c r="O11" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>6.36</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.74</v>
+        <v>1.44</v>
       </c>
       <c r="O12" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="P12" t="n">
-        <v>4.61</v>
+        <v>6</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.9</v>
+        <v>1.71</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>3.56</v>
       </c>
       <c r="P13" t="n">
-        <v>1.91</v>
+        <v>4.84</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2639,10 +2639,10 @@
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="R14" t="n">
         <v>1.91</v>
@@ -2654,16 +2654,16 @@
         <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
         <v>1.4</v>
@@ -2672,10 +2672,10 @@
         <v>2.8</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC14" t="n">
         <v>4.2</v>
@@ -2684,10 +2684,10 @@
         <v>1.2</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AG14" t="n">
         <v>1.83</v>
@@ -2792,22 +2792,22 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.63</v>
+        <v>5.24</v>
       </c>
       <c r="O15" t="n">
-        <v>3.28</v>
+        <v>3.57</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.82</v>
+        <v>4.66</v>
       </c>
       <c r="R15" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="S15" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="T15" t="n">
         <v>2.8</v>
@@ -2831,16 +2831,16 @@
         <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AC15" t="n">
         <v>3.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
         <v>1.07</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>2.07</v>
+        <v>1.19</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>5.25</v>
       </c>
       <c r="O17" t="n">
-        <v>5.25</v>
+        <v>4.2</v>
       </c>
       <c r="P17" t="n">
-        <v>7.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.73</v>
+        <v>5.61</v>
       </c>
       <c r="R17" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.18</v>
       </c>
-      <c r="T17" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.05</v>
+        <v>1.08</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.25</v>
+        <v>1.28</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.34</v>
+        <v>1.74</v>
       </c>
       <c r="R18" t="n">
-        <v>2.29</v>
+        <v>2.69</v>
       </c>
       <c r="S18" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="T18" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="U18" t="n">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="V18" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.5</v>
+        <v>6.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.52</v>
+        <v>1.27</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.24</v>
+        <v>3.14</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.34</v>
+        <v>1.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>2.75</v>
+        <v>1.08</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.05</v>
+        <v>3.3</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3428,28 +3428,28 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="O19" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="P19" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="S19" t="n">
         <v>1.27</v>
       </c>
       <c r="T19" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U19" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
         <v>1.5</v>
@@ -3464,16 +3464,16 @@
         <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.25</v>
+        <v>4.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="AD19" t="n">
         <v>1.47</v>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3587,19 +3587,19 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="O20" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P20" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="R20" t="n">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="S20" t="n">
         <v>1.25</v>
@@ -3608,10 +3608,10 @@
         <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="V20" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W20" t="n">
         <v>1.08</v>
@@ -3626,25 +3626,25 @@
         <v>4.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AC20" t="n">
         <v>2.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AE20" t="n">
         <v>1.15</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
         <v>1.9</v>
@@ -3746,19 +3746,19 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="O21" t="n">
-        <v>7.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R21" t="n">
-        <v>3.19</v>
+        <v>3.35</v>
       </c>
       <c r="S21" t="n">
         <v>1.17</v>
@@ -3767,13 +3767,13 @@
         <v>4.6</v>
       </c>
       <c r="U21" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
         <v>1.01</v>
@@ -3785,25 +3785,25 @@
         <v>7.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="AJ21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AK21" t="n">
-        <v>4.4</v>
+        <v>4.75</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.48</v>
+        <v>3.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="S24" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.65</v>
+        <v>7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.23</v>
+        <v>2.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,34 +4541,34 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="O26" t="n">
-        <v>4.95</v>
+        <v>7</v>
       </c>
       <c r="P26" t="n">
-        <v>7.75</v>
+        <v>17</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="R26" t="n">
-        <v>2.57</v>
+        <v>2.77</v>
       </c>
       <c r="S26" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="T26" t="n">
-        <v>3.9</v>
+        <v>3.22</v>
       </c>
       <c r="U26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V26" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
@@ -4577,28 +4577,28 @@
         <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.88</v>
+        <v>4.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.21</v>
+        <v>2.33</v>
       </c>
       <c r="AD26" t="n">
         <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.76</v>
+        <v>2.49</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>1.07</v>
       </c>
       <c r="AK26" t="n">
-        <v>3.2</v>
+        <v>5.05</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,34 +4700,34 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="O27" t="n">
-        <v>6.7</v>
+        <v>5.25</v>
       </c>
       <c r="P27" t="n">
-        <v>19.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="R27" t="n">
-        <v>3.04</v>
+        <v>2.47</v>
       </c>
       <c r="S27" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T27" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="U27" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V27" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
@@ -4736,28 +4736,28 @@
         <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.65</v>
+        <v>4.88</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.49</v>
+        <v>1.76</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.48</v>
+        <v>1.94</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AK27" t="n">
-        <v>5</v>
+        <v>2.82</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,46 +4859,46 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="O28" t="n">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P28" t="n">
         <v>4.55</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R28" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S28" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T28" t="n">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="U28" t="n">
-        <v>2.69</v>
+        <v>2.58</v>
       </c>
       <c r="V28" t="n">
         <v>1.4</v>
       </c>
       <c r="W28" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
         <v>1.24</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="AB28" t="n">
         <v>1.92</v>
@@ -4907,7 +4907,7 @@
         <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE28" t="n">
         <v>1.08</v>
@@ -4929,10 +4929,10 @@
         </is>
       </c>
       <c r="AJ28" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AK28" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -5018,10 +5018,10 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O29" t="n">
-        <v>2.61</v>
+        <v>2.75</v>
       </c>
       <c r="P29" t="n">
         <v>3.4</v>
@@ -5177,25 +5177,25 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="P30" t="n">
-        <v>3.7</v>
+        <v>3.78</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S30" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
         <v>3.58</v>
@@ -5204,10 +5204,10 @@
         <v>1.21</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X30" t="n">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="Y30" t="n">
         <v>1.54</v>
@@ -5216,16 +5216,16 @@
         <v>2.32</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AC30" t="n">
         <v>5.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AE30" t="n">
         <v>1.04</v>
@@ -5234,7 +5234,7 @@
         <v>2.21</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5247,10 +5247,10 @@
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="O31" t="n">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="P31" t="n">
-        <v>4.35</v>
+        <v>3.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.02</v>
+        <v>2.55</v>
       </c>
       <c r="R31" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="S31" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="T31" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="U31" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.45</v>
+        <v>3.01</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.63</v>
+        <v>2.16</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.46</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="AE31" t="n">
         <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="O32" t="n">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="P32" t="n">
-        <v>4.05</v>
+        <v>4.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="R32" t="n">
-        <v>1.98</v>
+        <v>1.77</v>
       </c>
       <c r="S32" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="T32" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="U32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA32" t="n">
         <v>3</v>
       </c>
-      <c r="V32" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X32" t="n">
+      <c r="AB32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y32" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AF32" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="S33" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T33" t="n">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="U33" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="V33" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X33" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE33" t="n">
         <v>1.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK33" t="n">
         <v>1.5</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>2.07</v>
       </c>
       <c r="O34" t="n">
-        <v>4.78</v>
+        <v>2.85</v>
       </c>
       <c r="P34" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.96</v>
+        <v>2.88</v>
       </c>
       <c r="R34" t="n">
-        <v>2.32</v>
+        <v>1.88</v>
       </c>
       <c r="S34" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3.6</v>
+        <v>2.16</v>
       </c>
       <c r="U34" t="n">
-        <v>2.31</v>
+        <v>3.95</v>
       </c>
       <c r="V34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.57</v>
       </c>
-      <c r="W34" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Z34" t="n">
-        <v>4.65</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.35</v>
+        <v>1.39</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.45</v>
+        <v>5.75</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.51</v>
+        <v>1.07</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.72</v>
+        <v>2.3</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
-        <v>2.84</v>
+        <v>4.78</v>
       </c>
       <c r="P35" t="n">
-        <v>3.85</v>
+        <v>6.75</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.8</v>
+        <v>1.83</v>
       </c>
       <c r="R35" t="n">
-        <v>1.78</v>
+        <v>2.6</v>
       </c>
       <c r="S35" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="T35" t="n">
-        <v>2.16</v>
+        <v>3.45</v>
       </c>
       <c r="U35" t="n">
-        <v>3.95</v>
+        <v>2.29</v>
       </c>
       <c r="V35" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="W35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X35" t="n">
         <v>1.01</v>
       </c>
-      <c r="X35" t="n">
+      <c r="Y35" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y35" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Z35" t="n">
-        <v>2.25</v>
+        <v>4.65</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.87</v>
+        <v>1.57</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.39</v>
+        <v>2.38</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.75</v>
+        <v>2.48</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.54</v>
+        <v>2</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.62</v>
+        <v>2.75</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -6170,10 +6170,10 @@
         <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="O37" t="n">
-        <v>2.45</v>
+        <v>3.27</v>
       </c>
       <c r="P37" t="n">
-        <v>4.26</v>
+        <v>3.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.12</v>
+        <v>2.39</v>
       </c>
       <c r="R37" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="S37" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="U37" t="n">
-        <v>4.4</v>
+        <v>2.81</v>
       </c>
       <c r="V37" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="W37" t="n">
         <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.25</v>
+        <v>2.09</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="AC37" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.89</v>
+        <v>2.43</v>
       </c>
       <c r="O38" t="n">
-        <v>3.45</v>
+        <v>3.22</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.12</v>
+        <v>1.72</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,65 +6608,65 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.11</v>
+        <v>2.19</v>
       </c>
       <c r="O39" t="n">
-        <v>3.38</v>
+        <v>2.6</v>
       </c>
       <c r="P39" t="n">
-        <v>3.68</v>
+        <v>4.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.56</v>
+        <v>3.14</v>
       </c>
       <c r="R39" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="S39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.42</v>
       </c>
-      <c r="T39" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U39" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AH39" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.78</v>
+        <v>1.55</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="O40" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="P40" t="n">
-        <v>2.57</v>
+        <v>3.45</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.72</v>
+        <v>2.19</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.07</v>
+        <v>1.68</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6926,37 +6926,37 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O41" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="P41" t="n">
-        <v>4.81</v>
+        <v>4.4</v>
       </c>
       <c r="Q41" t="n">
         <v>2.76</v>
       </c>
       <c r="R41" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S41" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="T41" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="U41" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="W41" t="n">
         <v>1.03</v>
       </c>
       <c r="X41" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y41" t="n">
         <v>1.65</v>
@@ -6968,7 +6968,7 @@
         <v>3.1</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AC41" t="n">
         <v>6.43</v>
@@ -6980,10 +6980,10 @@
         <v>1.02</v>
       </c>
       <c r="AF41" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -6996,10 +6996,10 @@
         </is>
       </c>
       <c r="AJ41" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>3.13</v>
+        <v>2.9</v>
       </c>
       <c r="O42" t="n">
-        <v>2.79</v>
+        <v>2.7</v>
       </c>
       <c r="P42" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.25</v>
+        <v>1.17</v>
       </c>
       <c r="O43" t="n">
-        <v>2.9</v>
+        <v>6</v>
       </c>
       <c r="P43" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.01</v>
+        <v>1.53</v>
       </c>
       <c r="R43" t="n">
-        <v>1.9</v>
+        <v>3.3</v>
       </c>
       <c r="S43" t="n">
-        <v>1.45</v>
+        <v>1.12</v>
       </c>
       <c r="T43" t="n">
-        <v>2.52</v>
+        <v>5.5</v>
       </c>
       <c r="U43" t="n">
-        <v>3.28</v>
+        <v>1.62</v>
       </c>
       <c r="V43" t="n">
-        <v>1.29</v>
+        <v>2.15</v>
       </c>
       <c r="W43" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X43" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y43" t="n">
         <v>1.03</v>
       </c>
-      <c r="X43" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z43" t="n">
-        <v>2.53</v>
+        <v>7.5</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.41</v>
+        <v>1.21</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.56</v>
+        <v>3.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.59</v>
+        <v>1.6</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.17</v>
+        <v>2.19</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.97</v>
+        <v>1.57</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.75</v>
+        <v>2.19</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.6</v>
+        <v>4.1</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.17</v>
+        <v>1.99</v>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>4.31</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="O45" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P45" t="n">
-        <v>4.26</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.62</v>
+        <v>3.01</v>
       </c>
       <c r="R45" t="n">
-        <v>2.13</v>
+        <v>1.9</v>
       </c>
       <c r="S45" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T45" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="U45" t="n">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="V45" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X45" t="n">
         <v>1.07</v>
       </c>
-      <c r="X45" t="n">
-        <v>1.02</v>
-      </c>
       <c r="Y45" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AC45" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.53</v>
+        <v>1.95</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="O46" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P46" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7880,16 +7880,16 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="O47" t="n">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="P47" t="n">
-        <v>6.85</v>
+        <v>6.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="R47" t="n">
         <v>2.4</v>
@@ -7898,13 +7898,13 @@
         <v>1.3</v>
       </c>
       <c r="T47" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="U47" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="V47" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="W47" t="n">
         <v>1.11</v>
@@ -7913,28 +7913,28 @@
         <v>1.04</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z47" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AA47" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AB47" t="n">
         <v>2.2</v>
       </c>
       <c r="AC47" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
         <v>1.91</v>
@@ -7953,7 +7953,7 @@
         <v>1.15</v>
       </c>
       <c r="AK47" t="n">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
@@ -8039,61 +8039,61 @@
         </is>
       </c>
       <c r="N48" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O48" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P48" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R48" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="S48" t="n">
         <v>1.25</v>
       </c>
       <c r="T48" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U48" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="V48" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W48" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X48" t="n">
         <v>1.03</v>
       </c>
       <c r="Y48" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AE48" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z48" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AF48" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AG48" t="n">
         <v>2.45</v>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK48" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.66</v>
+        <v>2.61</v>
       </c>
       <c r="R3" t="n">
-        <v>2.46</v>
+        <v>2.04</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>3.28</v>
+        <v>3.01</v>
       </c>
       <c r="U3" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB5" t="n">
         <v>2.02</v>
       </c>
-      <c r="O5" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AC5" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.77</v>
+        <v>1.11</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="O6" t="n">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="P6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R6" t="n">
+        <v>2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q6" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U6" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>4.56</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.05</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.82</v>
+        <v>2.49</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.88</v>
+        <v>4.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
         <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,80 +2792,80 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.24</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
-        <v>3.57</v>
+        <v>5.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.48</v>
+        <v>6.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.66</v>
+        <v>1.74</v>
       </c>
       <c r="R15" t="n">
-        <v>2.11</v>
+        <v>2.69</v>
       </c>
       <c r="S15" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="T15" t="n">
-        <v>2.8</v>
+        <v>3.85</v>
       </c>
       <c r="U15" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.83</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.27</v>
       </c>
       <c r="X15" t="n">
         <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="Z15" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK15" t="n">
         <v>3.3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.09</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.93</v>
+        <v>2.4</v>
       </c>
       <c r="O31" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="S31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.42</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z31" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,80 +5654,80 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="O33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R33" t="n">
+        <v>2</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U33" t="n">
         <v>3</v>
       </c>
-      <c r="P33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R33" t="n">
+      <c r="V33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF33" t="n">
         <v>1.95</v>
       </c>
-      <c r="S33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U33" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="AG33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="n">
         <v>1.21</v>
       </c>
-      <c r="AE33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AK33" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="O37" t="n">
-        <v>3.27</v>
+        <v>3.21</v>
       </c>
       <c r="P37" t="n">
-        <v>3.31</v>
+        <v>3.45</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="R37" t="n">
         <v>2.05</v>
       </c>
       <c r="S37" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T37" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U37" t="n">
-        <v>2.81</v>
+        <v>3.02</v>
       </c>
       <c r="V37" t="n">
         <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z37" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.09</v>
+        <v>2.19</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD37" t="n">
         <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF37" t="n">
         <v>1.85</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="O39" t="n">
-        <v>2.6</v>
+        <v>3.27</v>
       </c>
       <c r="P39" t="n">
-        <v>4.25</v>
+        <v>3.31</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.14</v>
+        <v>2.39</v>
       </c>
       <c r="R39" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="S39" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="T39" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="U39" t="n">
-        <v>4.4</v>
+        <v>2.81</v>
       </c>
       <c r="V39" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="W39" t="n">
         <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.25</v>
+        <v>2.09</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.42</v>
+        <v>1.83</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.55</v>
+        <v>1.89</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>2.19</v>
       </c>
       <c r="O40" t="n">
-        <v>3.21</v>
+        <v>2.6</v>
       </c>
       <c r="P40" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.44</v>
+        <v>3.14</v>
       </c>
       <c r="R40" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="S40" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="T40" t="n">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="U40" t="n">
-        <v>3.02</v>
+        <v>4.4</v>
       </c>
       <c r="V40" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="W40" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AD40" t="n">
         <v>1.05</v>
       </c>
-      <c r="X40" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE40" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.84</v>
+        <v>1.42</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="O44" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="P44" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.66</v>
+        <v>1.97</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
-        <v>3</v>
+        <v>4.31</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AC45" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="O46" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P46" t="n">
-        <v>4.26</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="R46" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="S46" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="U46" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE46" t="n">
         <v>1.05</v>
       </c>
-      <c r="X46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF46" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="O2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R2" t="n">
         <v>2.12</v>
@@ -776,13 +776,13 @@
         <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF2" t="n">
         <v>1.59</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.02</v>
+        <v>3.92</v>
       </c>
       <c r="O3" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P3" t="n">
-        <v>3.35</v>
+        <v>1.84</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.61</v>
+        <v>4.55</v>
       </c>
       <c r="R3" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T3" t="n">
-        <v>3.01</v>
+        <v>2.86</v>
       </c>
       <c r="U3" t="n">
-        <v>2.64</v>
+        <v>2.79</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W3" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AE3" t="n">
         <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.24</v>
+        <v>1.78</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.77</v>
+        <v>1.17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,80 +1043,80 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.92</v>
+        <v>2.02</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P4" t="n">
-        <v>1.84</v>
+        <v>3.35</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.55</v>
+        <v>2.61</v>
       </c>
       <c r="R4" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="S4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>2.86</v>
+        <v>3.01</v>
       </c>
       <c r="U4" t="n">
-        <v>2.79</v>
+        <v>2.64</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X4" t="n">
         <v>1.04</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y4" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.2</v>
+        <v>3.42</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE4" t="n">
         <v>1.1</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AG4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK4" t="n">
         <v>1.77</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.17</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,13 +2156,13 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3.78</v>
+        <v>1.71</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>4.84</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -2195,10 +2195,10 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.71</v>
+        <v>3.78</v>
       </c>
       <c r="O13" t="n">
-        <v>3.56</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>4.84</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2513,10 +2513,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4226,61 +4226,61 @@
         <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.74</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="S24" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,34 +4541,34 @@
         </is>
       </c>
       <c r="N26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O26" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P26" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.15</v>
-      </c>
-      <c r="O26" t="n">
-        <v>7</v>
-      </c>
-      <c r="P26" t="n">
-        <v>17</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R26" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.11</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
@@ -4577,28 +4577,28 @@
         <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.65</v>
+        <v>4.88</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.49</v>
+        <v>1.76</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.53</v>
+        <v>1.94</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK26" t="n">
-        <v>5.05</v>
+        <v>2.82</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,34 +4700,34 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="O27" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="P27" t="n">
-        <v>7.75</v>
+        <v>17</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.71</v>
+        <v>1.44</v>
       </c>
       <c r="R27" t="n">
-        <v>2.47</v>
+        <v>2.77</v>
       </c>
       <c r="S27" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T27" t="n">
-        <v>3.6</v>
+        <v>3.22</v>
       </c>
       <c r="U27" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="V27" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
@@ -4736,28 +4736,28 @@
         <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.88</v>
+        <v>4.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.76</v>
+        <v>2.49</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.94</v>
+        <v>1.53</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.82</v>
+        <v>5.05</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,80 +5336,80 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.4</v>
+        <v>1.93</v>
       </c>
       <c r="O31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="V31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF31" t="n">
         <v>1.95</v>
       </c>
-      <c r="S31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD31" t="n">
+      <c r="AG31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ31" t="n">
         <v>1.21</v>
       </c>
-      <c r="AE31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AK31" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,80 +5495,80 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.08</v>
+        <v>2.4</v>
       </c>
       <c r="O32" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>4.17</v>
+        <v>2.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="S32" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="T32" t="n">
-        <v>2.07</v>
+        <v>2.47</v>
       </c>
       <c r="U32" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
         <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AA32" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AC32" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.35</v>
+        <v>1.9</v>
       </c>
       <c r="AG32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK32" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.69</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="O33" t="n">
-        <v>2.98</v>
+        <v>2.83</v>
       </c>
       <c r="P33" t="n">
-        <v>3.2</v>
+        <v>4.17</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>1.77</v>
       </c>
       <c r="S33" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="T33" t="n">
-        <v>2.54</v>
+        <v>2.07</v>
       </c>
       <c r="U33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA33" t="n">
         <v>3</v>
       </c>
-      <c r="V33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.16</v>
-      </c>
       <c r="AB33" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.6</v>
+        <v>5.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.26</v>
+        <v>1.07</v>
       </c>
       <c r="AE33" t="n">
         <v>1.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,64 +5813,64 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>2.07</v>
+        <v>1.44</v>
       </c>
       <c r="O34" t="n">
-        <v>2.85</v>
+        <v>4.78</v>
       </c>
       <c r="P34" t="n">
-        <v>3.7</v>
+        <v>6.75</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="R34" t="n">
-        <v>1.88</v>
+        <v>2.6</v>
       </c>
       <c r="S34" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="T34" t="n">
-        <v>2.16</v>
+        <v>3.45</v>
       </c>
       <c r="U34" t="n">
-        <v>3.95</v>
+        <v>2.29</v>
       </c>
       <c r="V34" t="n">
-        <v>1.17</v>
+        <v>1.57</v>
       </c>
       <c r="W34" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X34" t="n">
         <v>1.01</v>
       </c>
-      <c r="X34" t="n">
+      <c r="Y34" t="n">
         <v>1.12</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Z34" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA34" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z34" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>2.87</v>
-      </c>
       <c r="AB34" t="n">
-        <v>1.39</v>
+        <v>2.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>5.75</v>
+        <v>2.48</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.3</v>
+        <v>1.73</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
         </is>
       </c>
       <c r="AJ34" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.63</v>
+        <v>2.75</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>1.44</v>
+        <v>2.07</v>
       </c>
       <c r="O35" t="n">
-        <v>4.78</v>
+        <v>2.85</v>
       </c>
       <c r="P35" t="n">
-        <v>6.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="R35" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="S35" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="T35" t="n">
-        <v>3.45</v>
+        <v>2.16</v>
       </c>
       <c r="U35" t="n">
-        <v>2.29</v>
+        <v>3.95</v>
       </c>
       <c r="V35" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="Y35" t="n">
         <v>1.57</v>
       </c>
-      <c r="W35" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Z35" t="n">
-        <v>4.65</v>
+        <v>2.25</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.57</v>
+        <v>2.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.38</v>
+        <v>1.39</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.48</v>
+        <v>5.75</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.55</v>
+        <v>1.07</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.1</v>
+        <v>1.32</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.75</v>
+        <v>1.63</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,80 +6131,80 @@
         </is>
       </c>
       <c r="N36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O36" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="P36" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK36" t="n">
         <v>1.8</v>
-      </c>
-      <c r="O36" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="P36" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="O37" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="P37" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="R37" t="n">
         <v>2.05</v>
       </c>
       <c r="S37" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T37" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U37" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="V37" t="n">
         <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD37" t="n">
         <v>1.22</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF37" t="n">
         <v>1.85</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="O38" t="n">
-        <v>3.22</v>
+        <v>2.6</v>
       </c>
       <c r="P38" t="n">
-        <v>2.56</v>
+        <v>4.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.72</v>
+        <v>3.25</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.07</v>
+        <v>1.33</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.94</v>
+        <v>2.43</v>
       </c>
       <c r="O39" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="P39" t="n">
-        <v>3.31</v>
+        <v>2.56</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.09</v>
+        <v>1.72</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="O40" t="n">
-        <v>2.6</v>
+        <v>3.44</v>
       </c>
       <c r="P40" t="n">
-        <v>4.25</v>
+        <v>3.91</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.25</v>
+        <v>1.7</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AC40" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,65 +7085,65 @@
         </is>
       </c>
       <c r="N42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O42" t="n">
         <v>2.9</v>
       </c>
-      <c r="O42" t="n">
-        <v>2.7</v>
-      </c>
       <c r="P42" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.98</v>
+        <v>3.01</v>
       </c>
       <c r="R42" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.75</v>
       </c>
-      <c r="S42" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U42" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X42" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AD42" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF42" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,65 +7403,65 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.87</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="P44" t="n">
-        <v>4.26</v>
+        <v>2.77</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="R44" t="n">
-        <v>2.15</v>
+        <v>1.88</v>
       </c>
       <c r="S44" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="U44" t="n">
-        <v>2.6</v>
+        <v>3.75</v>
       </c>
       <c r="V44" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB44" t="n">
         <v>1.4</v>
       </c>
-      <c r="W44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.97</v>
-      </c>
       <c r="AC44" t="n">
-        <v>2.75</v>
+        <v>5.3</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG44" t="n">
         <v>1.58</v>
       </c>
-      <c r="AG44" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,65 +7721,65 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="O46" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P46" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T46" t="n">
         <v>3</v>
       </c>
-      <c r="Q46" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S46" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T46" t="n">
-        <v>2.34</v>
-      </c>
       <c r="U46" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="V46" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="W46" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X46" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.35</v>
+        <v>1.66</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="AC46" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AF46" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG46" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG46" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.55</v>
+        <v>3.66</v>
       </c>
       <c r="R3" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="S3" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>2.86</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>2.79</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD3" t="n">
         <v>1.4</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.84</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.66</v>
+        <v>4.55</v>
       </c>
       <c r="R5" t="n">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="T5" t="n">
-        <v>3.28</v>
+        <v>2.86</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>2.79</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.33</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.68</v>
+        <v>1.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.84</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.8</v>
+        <v>3.46</v>
       </c>
       <c r="O6" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="S6" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="T6" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.05</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.82</v>
+        <v>2.49</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.88</v>
+        <v>4.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
         <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="P7" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.37</v>
-      </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.65</v>
+        <v>3.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
         <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.44</v>
+        <v>3.78</v>
       </c>
       <c r="O12" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.8</v>
+        <v>2.37</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,49 +2474,49 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.78</v>
+        <v>1.44</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB13" t="n">
         <v>2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
       <c r="O16" t="n">
-        <v>3.57</v>
+        <v>4.2</v>
       </c>
       <c r="P16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.66</v>
+        <v>5.61</v>
       </c>
       <c r="R16" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="S16" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>2.65</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.3</v>
+        <v>4.71</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.84</v>
+        <v>2.24</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.88</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.61</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.71</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,22 +3227,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3265,68 +3265,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.77</v>
+        <v>1.91</v>
       </c>
       <c r="O19" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="P19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T19" t="n">
         <v>3.6</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3.4</v>
-      </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W19" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.15</v>
       </c>
-      <c r="Z19" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="O20" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="P20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S20" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="V20" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AE20" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.15</v>
-      </c>
       <c r="AF20" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4226,61 +4226,61 @@
         <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>3.74</v>
       </c>
       <c r="R24" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="S24" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="T24" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="V24" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.65</v>
+        <v>7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5336,7 +5336,7 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="O31" t="n">
         <v>2.98</v>
@@ -5354,7 +5354,7 @@
         <v>1.42</v>
       </c>
       <c r="T31" t="n">
-        <v>2.54</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
         <v>3</v>
@@ -5369,7 +5369,7 @@
         <v>1.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
         <v>3.01</v>
@@ -5381,10 +5381,10 @@
         <v>1.65</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AE31" t="n">
         <v>1.03</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P32" t="n">
-        <v>2.8</v>
+        <v>4.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="R32" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="S32" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="T32" t="n">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="W32" t="n">
         <v>1.03</v>
       </c>
       <c r="X32" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.2</v>
+        <v>2.81</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.9</v>
+        <v>2.35</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,80 +5654,80 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="P33" t="n">
-        <v>4.17</v>
+        <v>2.58</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="S33" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="T33" t="n">
-        <v>2.07</v>
+        <v>2.47</v>
       </c>
       <c r="U33" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="V33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.18</v>
       </c>
-      <c r="W33" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AE33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK33" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.69</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="O36" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="P36" t="n">
-        <v>3.45</v>
+        <v>3.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="R36" t="n">
         <v>2.05</v>
       </c>
       <c r="S36" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T36" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U36" t="n">
-        <v>3.02</v>
+        <v>2.81</v>
       </c>
       <c r="V36" t="n">
         <v>1.36</v>
       </c>
       <c r="W36" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD36" t="n">
         <v>1.22</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF36" t="n">
         <v>1.85</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="O37" t="n">
-        <v>3.27</v>
+        <v>2.6</v>
       </c>
       <c r="P37" t="n">
-        <v>3.31</v>
+        <v>4.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.39</v>
+        <v>3.14</v>
       </c>
       <c r="R37" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="S37" t="n">
-        <v>1.43</v>
+        <v>1.62</v>
       </c>
       <c r="T37" t="n">
-        <v>2.62</v>
+        <v>2.2</v>
       </c>
       <c r="U37" t="n">
-        <v>2.81</v>
+        <v>4.4</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="W37" t="n">
         <v>1.02</v>
       </c>
       <c r="X37" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.09</v>
+        <v>3.25</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.78</v>
+        <v>1.33</v>
       </c>
       <c r="AC37" t="n">
-        <v>3.5</v>
+        <v>6.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.85</v>
+        <v>2.57</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.89</v>
+        <v>1.55</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA38" t="n">
         <v>2.19</v>
       </c>
-      <c r="O38" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P38" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="T38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U38" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Y38" t="n">
+      <c r="AB38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK38" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1.55</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,13 +6608,13 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.43</v>
+        <v>1.8</v>
       </c>
       <c r="O39" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="P39" t="n">
-        <v>2.56</v>
+        <v>3.91</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.8</v>
+        <v>2.43</v>
       </c>
       <c r="O40" t="n">
-        <v>3.44</v>
+        <v>3.22</v>
       </c>
       <c r="P40" t="n">
-        <v>3.91</v>
+        <v>2.56</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
@@ -6806,10 +6806,10 @@
         <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,65 +7085,65 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="O42" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P42" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T42" t="n">
         <v>3</v>
       </c>
-      <c r="Q42" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R42" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S42" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T42" t="n">
-        <v>2.34</v>
-      </c>
       <c r="U42" t="n">
-        <v>3.3</v>
+        <v>2.56</v>
       </c>
       <c r="V42" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="W42" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X42" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.53</v>
+        <v>3.42</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.55</v>
+        <v>1.88</v>
       </c>
       <c r="AC42" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF42" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG42" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG42" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,65 +7244,65 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.17</v>
+        <v>2.7</v>
       </c>
       <c r="O43" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="P43" t="n">
-        <v>13</v>
+        <v>2.79</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.53</v>
+        <v>3.74</v>
       </c>
       <c r="R43" t="n">
-        <v>3.3</v>
+        <v>1.75</v>
       </c>
       <c r="S43" t="n">
-        <v>1.12</v>
+        <v>1.63</v>
       </c>
       <c r="T43" t="n">
-        <v>5.5</v>
+        <v>2.13</v>
       </c>
       <c r="U43" t="n">
-        <v>1.62</v>
+        <v>3.78</v>
       </c>
       <c r="V43" t="n">
-        <v>2.15</v>
+        <v>1.19</v>
       </c>
       <c r="W43" t="n">
-        <v>1.32</v>
+        <v>1.04</v>
       </c>
       <c r="X43" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y43" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AE43" t="n">
         <v>1.03</v>
       </c>
-      <c r="Z43" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC43" t="n">
+      <c r="AF43" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG43" t="n">
         <v>1.6</v>
       </c>
-      <c r="AD43" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>2.19</v>
-      </c>
       <c r="AH43" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="AK43" t="n">
-        <v>4.1</v>
+        <v>1.39</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>1.99</v>
       </c>
       <c r="O44" t="n">
-        <v>2.65</v>
+        <v>2.95</v>
       </c>
       <c r="P44" t="n">
-        <v>2.77</v>
+        <v>4.31</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="AC44" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.99</v>
+        <v>1.17</v>
       </c>
       <c r="O45" t="n">
-        <v>2.95</v>
+        <v>6</v>
       </c>
       <c r="P45" t="n">
-        <v>4.31</v>
+        <v>13</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>1.21</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>3.5</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="O46" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P46" t="n">
-        <v>4.26</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.4</v>
+        <v>3.06</v>
       </c>
       <c r="R46" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="S46" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T46" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="U46" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="V46" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="W46" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X46" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.66</v>
+        <v>2.25</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.97</v>
+        <v>1.53</v>
       </c>
       <c r="AC46" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -725,25 +725,25 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="O2" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="U2" t="n">
         <v>2.4</v>
@@ -755,19 +755,19 @@
         <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AC2" t="n">
         <v>2.78</v>
@@ -779,10 +779,10 @@
         <v>1.13</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.24</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
         <v>4.33</v>
@@ -926,7 +926,7 @@
         <v>1.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="AC3" t="n">
         <v>2.7</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.02</v>
+        <v>3.83</v>
       </c>
       <c r="O4" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.61</v>
+        <v>4.72</v>
       </c>
       <c r="R4" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="S4" t="n">
         <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.23</v>
       </c>
-      <c r="Z4" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.77</v>
+        <v>1.18</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.92</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AA5" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q5" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="R5" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
         <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.17</v>
+        <v>1.64</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.46</v>
+        <v>3.58</v>
       </c>
       <c r="O6" t="n">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.15</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.56</v>
+        <v>4.48</v>
       </c>
       <c r="R6" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="U6" t="n">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.04</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.37</v>
+        <v>2.06</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.65</v>
+        <v>3.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AE6" t="n">
         <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.05</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.2</v>
+        <v>4.56</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="S7" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.05</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.82</v>
+        <v>2.49</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.15</v>
+        <v>2.41</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.88</v>
+        <v>4.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
         <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="O8" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>6.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="R8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T8" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="U8" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="V8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X8" t="n">
         <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.46</v>
+        <v>4.21</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="O9" t="n">
         <v>4.8</v>
@@ -1853,10 +1853,10 @@
         <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="T9" t="n">
-        <v>4.5</v>
+        <v>3.84</v>
       </c>
       <c r="U9" t="n">
         <v>2.03</v>
@@ -1874,13 +1874,13 @@
         <v>1.08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="AC9" t="n">
         <v>2.1</v>
@@ -1892,7 +1892,7 @@
         <v>1.28</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG9" t="n">
         <v>2.2</v>
@@ -2000,22 +2000,22 @@
         <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
         <v>2.42</v>
       </c>
       <c r="S10" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T10" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
         <v>1.99</v>
@@ -2024,22 +2024,22 @@
         <v>1.75</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Z10" t="n">
-        <v>6.18</v>
+        <v>6.27</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="AC10" t="n">
         <v>2</v>
@@ -2048,13 +2048,13 @@
         <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="AK10" t="n">
         <v>1.35</v>
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="O11" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>4.84</v>
+        <v>4.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.78</v>
+        <v>1.64</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>4.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.37</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.44</v>
+        <v>4.35</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>1.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.8</v>
+        <v>2.47</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,31 +2633,31 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="S14" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="U14" t="n">
         <v>3.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W14" t="n">
         <v>1.02</v>
@@ -2666,16 +2666,16 @@
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AC14" t="n">
         <v>4.2</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2788,68 +2788,68 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2951,16 +2951,16 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.25</v>
+        <v>5.64</v>
       </c>
       <c r="O16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.61</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
         <v>2.4</v>
@@ -2969,13 +2969,13 @@
         <v>1.25</v>
       </c>
       <c r="T16" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="U16" t="n">
         <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W16" t="n">
         <v>1.14</v>
@@ -2999,16 +2999,16 @@
         <v>2.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AE16" t="n">
         <v>1.18</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK16" t="n">
         <v>1.08</v>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3078,12 +3078,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3106,68 +3106,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3278,19 +3278,19 @@
         <v>1.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.66</v>
+        <v>5.82</v>
       </c>
       <c r="R18" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
         <v>1.4</v>
@@ -3305,13 +3305,13 @@
         <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
         <v>3.14</v>
@@ -3320,10 +3320,10 @@
         <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AG18" t="n">
         <v>1.88</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="O19" t="n">
-        <v>3.68</v>
+        <v>3.95</v>
       </c>
       <c r="P19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S19" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.33</v>
+        <v>4.52</v>
       </c>
       <c r="AA19" t="n">
         <v>1.64</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,25 +3587,25 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="O20" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R20" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="U20" t="n">
         <v>2.4</v>
@@ -3614,37 +3614,37 @@
         <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.52</v>
+        <v>4.33</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="AD20" t="n">
         <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3746,31 +3746,31 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="O21" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="Q21" t="n">
         <v>1.44</v>
       </c>
       <c r="R21" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="S21" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T21" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="U21" t="n">
         <v>1.84</v>
       </c>
       <c r="V21" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="W21" t="n">
         <v>1.25</v>
@@ -3791,10 +3791,10 @@
         <v>3.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AE21" t="n">
         <v>1.42</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O24" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.74</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="S24" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="U24" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X24" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AC24" t="n">
-        <v>7</v>
+        <v>5.65</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.51</v>
+        <v>2.25</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4541,34 +4541,34 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="O26" t="n">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="P26" t="n">
-        <v>7.75</v>
+        <v>17</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="R26" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="S26" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T26" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U26" t="n">
         <v>2.2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W26" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="X26" t="n">
         <v>1.02</v>
@@ -4577,28 +4577,28 @@
         <v>1.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.88</v>
+        <v>4.65</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.76</v>
+        <v>2.63</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.94</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4611,10 +4611,10 @@
         </is>
       </c>
       <c r="AJ26" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK26" t="n">
-        <v>2.82</v>
+        <v>5.05</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4668,12 +4668,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4700,34 +4700,34 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="O27" t="n">
+        <v>5</v>
+      </c>
+      <c r="P27" t="n">
         <v>7</v>
       </c>
-      <c r="P27" t="n">
-        <v>17</v>
-      </c>
       <c r="Q27" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="R27" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="S27" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T27" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="U27" t="n">
         <v>2.25</v>
       </c>
       <c r="V27" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
@@ -4736,28 +4736,28 @@
         <v>1.12</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AD27" t="n">
         <v>1.57</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.49</v>
+        <v>1.78</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4770,10 +4770,10 @@
         </is>
       </c>
       <c r="AJ27" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AK27" t="n">
-        <v>5.05</v>
+        <v>3.05</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4859,13 +4859,13 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O28" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="P28" t="n">
-        <v>4.55</v>
+        <v>4.8</v>
       </c>
       <c r="Q28" t="n">
         <v>2.2</v>
@@ -4877,7 +4877,7 @@
         <v>1.33</v>
       </c>
       <c r="T28" t="n">
-        <v>2.74</v>
+        <v>2.99</v>
       </c>
       <c r="U28" t="n">
         <v>2.58</v>
@@ -4898,19 +4898,19 @@
         <v>3.34</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
         <v>1.92</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD28" t="n">
         <v>1.28</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF28" t="n">
         <v>1.91</v>
@@ -5021,10 +5021,10 @@
         <v>2.3</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="P29" t="n">
-        <v>3.4</v>
+        <v>3.03</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -5177,10 +5177,10 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="O30" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="P30" t="n">
         <v>3.78</v>
@@ -5195,7 +5195,7 @@
         <v>1.58</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="U30" t="n">
         <v>3.58</v>
@@ -5225,7 +5225,7 @@
         <v>5.05</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AE30" t="n">
         <v>1.04</v>
@@ -5234,7 +5234,7 @@
         <v>2.21</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.89</v>
+        <v>2.2</v>
       </c>
       <c r="O31" t="n">
         <v>2.98</v>
       </c>
       <c r="P31" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U31" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U31" t="n">
-        <v>3</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X31" t="n">
         <v>1.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.21</v>
+        <v>1.36</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.85</v>
+        <v>1.5</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5498,7 +5498,7 @@
         <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="P32" t="n">
         <v>4.25</v>
@@ -5519,10 +5519,10 @@
         <v>3.9</v>
       </c>
       <c r="V32" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
         <v>1.14</v>
@@ -5534,10 +5534,10 @@
         <v>2.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
         <v>5.75</v>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="O33" t="n">
-        <v>2.98</v>
+        <v>3.24</v>
       </c>
       <c r="P33" t="n">
-        <v>2.58</v>
+        <v>4</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="R33" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="T33" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="U33" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V33" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W33" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X33" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.8</v>
+        <v>3.01</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC33" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Ferro Carril Oeste</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Colón</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5813,80 +5813,80 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="O34" t="n">
-        <v>4.78</v>
+        <v>2.75</v>
       </c>
       <c r="P34" t="n">
-        <v>6.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.83</v>
+        <v>2.89</v>
       </c>
       <c r="R34" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="S34" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="T34" t="n">
-        <v>3.45</v>
+        <v>2.24</v>
       </c>
       <c r="U34" t="n">
-        <v>2.29</v>
+        <v>3.95</v>
       </c>
       <c r="V34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y34" t="n">
         <v>1.57</v>
       </c>
-      <c r="W34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Z34" t="n">
-        <v>4.65</v>
+        <v>2.25</v>
       </c>
       <c r="AA34" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AK34" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>2.75</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ferro Carril Oeste</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Colón</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5972,64 +5972,64 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>2.07</v>
+        <v>1.44</v>
       </c>
       <c r="O35" t="n">
-        <v>2.85</v>
+        <v>4.6</v>
       </c>
       <c r="P35" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.88</v>
+        <v>1.9</v>
       </c>
       <c r="R35" t="n">
-        <v>1.88</v>
+        <v>2.45</v>
       </c>
       <c r="S35" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="T35" t="n">
-        <v>2.16</v>
+        <v>3.6</v>
       </c>
       <c r="U35" t="n">
-        <v>3.95</v>
+        <v>2.23</v>
       </c>
       <c r="V35" t="n">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="W35" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X35" t="n">
         <v>1.01</v>
       </c>
-      <c r="X35" t="n">
-        <v>1.12</v>
-      </c>
       <c r="Y35" t="n">
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.25</v>
+        <v>4.65</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.87</v>
+        <v>1.59</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.39</v>
+        <v>2.38</v>
       </c>
       <c r="AC35" t="n">
-        <v>5.75</v>
+        <v>2.45</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.3</v>
+        <v>1.71</v>
       </c>
       <c r="AG35" t="n">
-        <v>1.6</v>
+        <v>1.99</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6042,10 +6042,10 @@
         </is>
       </c>
       <c r="AJ35" t="n">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.63</v>
+        <v>2.62</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="O36" t="n">
-        <v>3.27</v>
+        <v>2.6</v>
       </c>
       <c r="P36" t="n">
-        <v>3.31</v>
+        <v>4.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="S36" t="n">
-        <v>1.43</v>
+        <v>1.82</v>
       </c>
       <c r="T36" t="n">
-        <v>2.62</v>
+        <v>1.88</v>
       </c>
       <c r="U36" t="n">
-        <v>2.81</v>
+        <v>4.4</v>
       </c>
       <c r="V36" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="W36" t="n">
         <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.29</v>
+        <v>1.77</v>
       </c>
       <c r="Z36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.09</v>
+        <v>3.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.78</v>
+        <v>1.26</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.5</v>
+        <v>6.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.83</v>
+        <v>1.42</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.19</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="P37" t="n">
-        <v>4.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.14</v>
+        <v>2.94</v>
       </c>
       <c r="R37" t="n">
-        <v>1.76</v>
+        <v>2.16</v>
       </c>
       <c r="S37" t="n">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>3.11</v>
       </c>
       <c r="U37" t="n">
-        <v>4.4</v>
+        <v>2.51</v>
       </c>
       <c r="V37" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="W37" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>3.25</v>
+        <v>1.71</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="AC37" t="n">
-        <v>6.5</v>
+        <v>2.74</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.05</v>
+        <v>1.39</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.02</v>
+        <v>1.13</v>
       </c>
       <c r="AF37" t="n">
-        <v>2.57</v>
+        <v>1.57</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.42</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="O38" t="n">
-        <v>3.21</v>
+        <v>3.44</v>
       </c>
       <c r="P38" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.44</v>
+        <v>2.37</v>
       </c>
       <c r="R38" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="V38" t="n">
         <v>1.44</v>
       </c>
-      <c r="T38" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U38" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.36</v>
-      </c>
       <c r="W38" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.1</v>
+        <v>3.86</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.19</v>
+        <v>1.69</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.8</v>
+        <v>2.62</v>
       </c>
       <c r="AD38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE38" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK38" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="O39" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="R39" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AK39" t="n">
         <v>1.8</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="P39" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>2.43</v>
+        <v>1.95</v>
       </c>
       <c r="O40" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="P40" t="n">
-        <v>2.56</v>
+        <v>3.9</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.72</v>
+        <v>2.09</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6926,28 +6926,28 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="O41" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P41" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="R41" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="S41" t="n">
         <v>1.57</v>
       </c>
       <c r="T41" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U41" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="V41" t="n">
         <v>1.22</v>
@@ -6959,10 +6959,10 @@
         <v>1.1</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Z41" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AA41" t="n">
         <v>3.1</v>
@@ -6971,10 +6971,10 @@
         <v>1.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>6.43</v>
+        <v>6.15</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AE41" t="n">
         <v>1.02</v>
@@ -6999,7 +6999,7 @@
         <v>1.33</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -7094,10 +7094,10 @@
         <v>4.26</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="R42" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="S42" t="n">
         <v>1.33</v>
@@ -7106,10 +7106,10 @@
         <v>3</v>
       </c>
       <c r="U42" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V42" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W42" t="n">
         <v>1.05</v>
@@ -7118,22 +7118,22 @@
         <v>1.02</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="AC42" t="n">
         <v>2.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE42" t="n">
         <v>1.08</v>
@@ -7158,7 +7158,7 @@
         <v>1.34</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.7</v>
+        <v>2.25</v>
       </c>
       <c r="O43" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P43" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.74</v>
+        <v>3.01</v>
       </c>
       <c r="R43" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="S43" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="T43" t="n">
-        <v>2.13</v>
+        <v>2.34</v>
       </c>
       <c r="U43" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="V43" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="W43" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.32</v>
+        <v>2.78</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.63</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AC43" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AE43" t="n">
         <v>1.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7314,10 +7314,10 @@
         </is>
       </c>
       <c r="AJ43" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.39</v>
+        <v>1.55</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.99</v>
+        <v>1.17</v>
       </c>
       <c r="O44" t="n">
-        <v>2.95</v>
+        <v>6.5</v>
       </c>
       <c r="P44" t="n">
-        <v>4.31</v>
+        <v>10</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.05</v>
+        <v>1.21</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.66</v>
+        <v>3.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.17</v>
+        <v>1.99</v>
       </c>
       <c r="O45" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="P45" t="n">
-        <v>13</v>
+        <v>4.31</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="AB45" t="n">
-        <v>3.5</v>
+        <v>1.66</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="O46" t="n">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>2.77</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.06</v>
+        <v>3.74</v>
       </c>
       <c r="R46" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="S46" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="T46" t="n">
-        <v>2.34</v>
+        <v>2.11</v>
       </c>
       <c r="U46" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="V46" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="W46" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE46" t="n">
         <v>1.03</v>
       </c>
-      <c r="X46" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF46" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -7880,10 +7880,10 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="O47" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="P47" t="n">
         <v>6.5</v>
@@ -7898,10 +7898,10 @@
         <v>1.3</v>
       </c>
       <c r="T47" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="U47" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="V47" t="n">
         <v>1.5</v>
@@ -7910,13 +7910,13 @@
         <v>1.11</v>
       </c>
       <c r="X47" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y47" t="n">
         <v>1.18</v>
       </c>
       <c r="Z47" t="n">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="AA47" t="n">
         <v>1.65</v>
@@ -7934,7 +7934,7 @@
         <v>1.17</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG47" t="n">
         <v>1.91</v>
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="AJ47" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK47" t="n">
         <v>2.6</v>
@@ -8045,7 +8045,7 @@
         <v>3.4</v>
       </c>
       <c r="P48" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q48" t="n">
         <v>3</v>
@@ -8072,31 +8072,31 @@
         <v>1.03</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z48" t="n">
-        <v>4.65</v>
+        <v>5.3</v>
       </c>
       <c r="AA48" t="n">
         <v>1.6</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AC48" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="AD48" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AG48" t="n">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.66</v>
+        <v>2.63</v>
       </c>
       <c r="R3" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="S3" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
-        <v>3.28</v>
+        <v>2.65</v>
       </c>
       <c r="U3" t="n">
-        <v>2.34</v>
+        <v>2.63</v>
       </c>
       <c r="V3" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="W3" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.33</v>
+        <v>3.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.68</v>
+        <v>1.84</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.63</v>
+        <v>3.66</v>
       </c>
       <c r="R5" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>3.28</v>
       </c>
       <c r="U5" t="n">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P6" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.48</v>
+        <v>4.56</v>
       </c>
       <c r="R6" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="T6" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="U6" t="n">
-        <v>3.14</v>
+        <v>3.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.1</v>
+        <v>2.49</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.06</v>
+        <v>2.41</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.6</v>
+        <v>4.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AE6" t="n">
         <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.78</v>
+        <v>2.01</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="O7" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.56</v>
+        <v>4.48</v>
       </c>
       <c r="R7" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>3.48</v>
+        <v>3.14</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.04</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.49</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.41</v>
+        <v>2.06</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.65</v>
+        <v>3.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.24</v>
       </c>
       <c r="AE7" t="n">
         <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.01</v>
+        <v>1.78</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Henan Jianye</t>
+          <t>Beijing Guoan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="O8" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P8" t="n">
-        <v>6.7</v>
+        <v>5.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="S8" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T8" t="n">
-        <v>3.42</v>
+        <v>3.84</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.03</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="W8" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.21</v>
+        <v>5.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.65</v>
+        <v>2.49</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beijing Guoan</t>
+          <t>Henan Jianye</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="O9" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="P9" t="n">
-        <v>5.75</v>
+        <v>6.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
-        <v>3.84</v>
+        <v>3.42</v>
       </c>
       <c r="U9" t="n">
-        <v>2.03</v>
+        <v>2.32</v>
       </c>
       <c r="V9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF9" t="n">
         <v>1.72</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AG9" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.49</v>
+        <v>2.65</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>5.64</v>
+        <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="S16" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="U16" t="n">
-        <v>2.34</v>
+        <v>1.78</v>
       </c>
       <c r="V16" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="W16" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.71</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.08</v>
+        <v>3.02</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>5.64</v>
       </c>
       <c r="O17" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="P17" t="n">
-        <v>6.75</v>
+        <v>1.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T17" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>2.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="W17" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.5</v>
+        <v>4.71</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.08</v>
+        <v>2.24</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.96</v>
+        <v>1.54</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.02</v>
+        <v>1.08</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="O19" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.3</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="AD19" t="n">
         <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>4.52</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="AD20" t="n">
         <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.65</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O32" t="n">
-        <v>2.63</v>
+        <v>3.24</v>
       </c>
       <c r="P32" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="R32" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S32" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="U32" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="V32" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X32" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.12</v>
+        <v>3.01</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.83</v>
+        <v>2.16</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC32" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE32" t="n">
         <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,64 +5654,64 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="O33" t="n">
-        <v>3.24</v>
+        <v>2.63</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S33" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="T33" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="V33" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="W33" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X33" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.01</v>
+        <v>2.12</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.16</v>
+        <v>2.83</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AE33" t="n">
         <v>1.03</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="AJ33" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="O36" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="P36" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q36" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R36" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U36" t="n">
         <v>3</v>
       </c>
-      <c r="R36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="T36" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U36" t="n">
-        <v>4.4</v>
-      </c>
       <c r="V36" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="W36" t="n">
         <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.77</v>
+        <v>1.29</v>
       </c>
       <c r="Z36" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="AA36" t="n">
-        <v>3.6</v>
+        <v>2.09</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AC36" t="n">
-        <v>6.55</v>
+        <v>3.68</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.05</v>
+        <v>1.28</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF36" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="O38" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="P38" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="S38" t="n">
-        <v>1.32</v>
+        <v>1.82</v>
       </c>
       <c r="T38" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="U38" t="n">
-        <v>2.47</v>
+        <v>4.4</v>
       </c>
       <c r="V38" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.44</v>
       </c>
-      <c r="W38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK38" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="O39" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P39" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.56</v>
+        <v>2.37</v>
       </c>
       <c r="R39" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S39" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T39" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="U39" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="V39" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W39" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X39" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.24</v>
+        <v>3.86</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AC39" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="AD39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE39" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,31 +6767,31 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="O40" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P40" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="R40" t="n">
         <v>2.05</v>
       </c>
       <c r="S40" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T40" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="U40" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="V40" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W40" t="n">
         <v>1.02</v>
@@ -6800,25 +6800,25 @@
         <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.05</v>
+        <v>3.24</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.68</v>
+        <v>3.9</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF40" t="n">
         <v>1.85</v>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.87</v>
+        <v>1.99</v>
       </c>
       <c r="O42" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="P42" t="n">
-        <v>4.26</v>
+        <v>4.31</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.64</v>
+        <v>2.05</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AC42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,80 +7403,80 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.17</v>
+        <v>1.87</v>
       </c>
       <c r="O44" t="n">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="P44" t="n">
-        <v>10</v>
+        <v>4.26</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="R44" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="S44" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="T44" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>1.62</v>
+        <v>2.6</v>
       </c>
       <c r="V44" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="W44" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="X44" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="AB44" t="n">
-        <v>3.5</v>
+        <v>1.69</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.6</v>
+        <v>2.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>2.19</v>
+        <v>1.36</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.51</v>
+        <v>1.08</v>
       </c>
       <c r="AF44" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AK44" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>4.1</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="O45" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="P45" t="n">
-        <v>4.31</v>
+        <v>2.77</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>2.62</v>
+        <v>1.16</v>
       </c>
       <c r="O46" t="n">
-        <v>2.78</v>
+        <v>6.25</v>
       </c>
       <c r="P46" t="n">
-        <v>2.77</v>
+        <v>9.75</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.74</v>
+        <v>1.55</v>
       </c>
       <c r="R46" t="n">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="S46" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="T46" t="n">
-        <v>2.11</v>
+        <v>4.75</v>
       </c>
       <c r="U46" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="V46" t="n">
-        <v>1.19</v>
+        <v>1.91</v>
       </c>
       <c r="W46" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="X46" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="Z46" t="n">
-        <v>2.55</v>
+        <v>7.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.63</v>
+        <v>1.31</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.43</v>
+        <v>2.92</v>
       </c>
       <c r="AC46" t="n">
-        <v>5.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF46" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.83</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.72</v>
+        <v>3.66</v>
       </c>
       <c r="R4" t="n">
-        <v>2.03</v>
+        <v>2.46</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T4" t="n">
-        <v>2.88</v>
+        <v>3.28</v>
       </c>
       <c r="U4" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="V4" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="X4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.1</v>
+        <v>4.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.8</v>
+        <v>2.21</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.66</v>
+        <v>4.72</v>
       </c>
       <c r="R5" t="n">
-        <v>2.46</v>
+        <v>2.03</v>
       </c>
       <c r="S5" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="U5" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="V5" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="P11" t="n">
-        <v>4.95</v>
+        <v>4.56</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="S11" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="T11" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>3.14</v>
+        <v>2.73</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.04</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.14</v>
+        <v>3.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.62</v>
+        <v>1.9</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.64</v>
+        <v>4.35</v>
       </c>
       <c r="O12" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>4.56</v>
+        <v>1.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.16</v>
+        <v>5.1</v>
       </c>
       <c r="R12" t="n">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
       <c r="S12" t="n">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="U12" t="n">
-        <v>2.73</v>
+        <v>3.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.8</v>
+        <v>2.64</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>2.47</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.9</v>
+        <v>1.51</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.1</v>
+        <v>4.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.79</v>
+        <v>1.62</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.14</v>
+        <v>1.31</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.15</v>
+        <v>1.18</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.35</v>
+        <v>1.67</v>
       </c>
       <c r="O13" t="n">
         <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>1.71</v>
+        <v>4.95</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T13" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="U13" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.64</v>
+        <v>3.14</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.18</v>
+        <v>2.01</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2788,68 +2788,68 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.24</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.64</v>
+        <v>1.28</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5</v>
+        <v>6.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T17" t="n">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="U17" t="n">
-        <v>2.34</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
-        <v>1.54</v>
+        <v>1.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.71</v>
+        <v>8.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.24</v>
+        <v>3.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.08</v>
+        <v>3.02</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.24</v>
+        <v>5.64</v>
       </c>
       <c r="O18" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q18" t="n">
-        <v>5.82</v>
+        <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="S18" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>2.75</v>
+        <v>2.34</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.2</v>
+        <v>4.71</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.87</v>
+        <v>2.24</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.14</v>
+        <v>2.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.89</v>
+        <v>1.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3863,22 +3863,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4032,12 +4032,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportivo Maipú</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O23" t="n">
         <v>2.5</v>
       </c>
-      <c r="O23" t="n">
-        <v>2.7</v>
-      </c>
       <c r="P23" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>3.64</v>
       </c>
       <c r="R23" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="S23" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="T23" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="U23" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AC23" t="n">
-        <v>5.65</v>
+        <v>6.95</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.25</v>
+        <v>2.51</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4191,12 +4191,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Deportivo Maipú</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -4382,64 +4382,64 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4452,10 +4452,10 @@
         </is>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ceará</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="O31" t="n">
-        <v>2.98</v>
+        <v>2.63</v>
       </c>
       <c r="P31" t="n">
-        <v>2.87</v>
+        <v>4.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="R31" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="S31" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="T31" t="n">
-        <v>2.47</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="V31" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.42</v>
+        <v>1.63</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.8</v>
+        <v>2.12</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.2</v>
+        <v>2.83</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5622,12 +5622,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Ceará</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5654,80 +5654,80 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="O33" t="n">
-        <v>2.63</v>
+        <v>2.98</v>
       </c>
       <c r="P33" t="n">
-        <v>4.25</v>
+        <v>2.87</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="S33" t="n">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.47</v>
       </c>
       <c r="U33" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X33" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="Z33" t="n">
-        <v>2.12</v>
+        <v>2.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.83</v>
+        <v>2.2</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="AC33" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.35</v>
+        <v>1.86</v>
       </c>
       <c r="AG33" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK33" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.57</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="O37" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="P37" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.94</v>
+        <v>2.37</v>
       </c>
       <c r="R37" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="S37" t="n">
         <v>1.32</v>
       </c>
       <c r="T37" t="n">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="U37" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="V37" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z37" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,64 +6449,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O38" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="P38" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="R38" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="S38" t="n">
-        <v>1.82</v>
+        <v>1.42</v>
       </c>
       <c r="T38" t="n">
-        <v>1.88</v>
+        <v>2.82</v>
       </c>
       <c r="U38" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="V38" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W38" t="n">
         <v>1.02</v>
       </c>
       <c r="X38" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="Z38" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="AA38" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AC38" t="n">
-        <v>6.55</v>
+        <v>3.9</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF38" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6519,10 +6519,10 @@
         </is>
       </c>
       <c r="AJ38" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK38" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,80 +6608,80 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="O39" t="n">
-        <v>3.44</v>
+        <v>2.6</v>
       </c>
       <c r="P39" t="n">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>2.13</v>
+        <v>1.63</v>
       </c>
       <c r="S39" t="n">
-        <v>1.32</v>
+        <v>1.82</v>
       </c>
       <c r="T39" t="n">
-        <v>2.92</v>
+        <v>1.88</v>
       </c>
       <c r="U39" t="n">
-        <v>2.47</v>
+        <v>4.4</v>
       </c>
       <c r="V39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39" t="n">
         <v>1.44</v>
       </c>
-      <c r="W39" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AK39" t="n">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="O40" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P40" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.56</v>
+        <v>2.94</v>
       </c>
       <c r="R40" t="n">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
       <c r="S40" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T40" t="n">
-        <v>2.82</v>
+        <v>3.11</v>
       </c>
       <c r="U40" t="n">
-        <v>2.9</v>
+        <v>2.51</v>
       </c>
       <c r="V40" t="n">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="W40" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X40" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="Z40" t="n">
-        <v>3.24</v>
+        <v>4</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="AC40" t="n">
-        <v>3.9</v>
+        <v>2.74</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.22</v>
+        <v>1.39</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.8</v>
+        <v>1.45</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="O42" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="P42" t="n">
-        <v>4.31</v>
+        <v>2.77</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="O43" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="P43" t="n">
+        <v>4.26</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T43" t="n">
         <v>3</v>
       </c>
-      <c r="Q43" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="R43" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T43" t="n">
-        <v>2.34</v>
-      </c>
       <c r="U43" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="V43" t="n">
-        <v>1.29</v>
+        <v>1.42</v>
       </c>
       <c r="W43" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X43" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="Z43" t="n">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="AA43" t="n">
-        <v>2.25</v>
+        <v>1.64</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AC43" t="n">
-        <v>4.5</v>
+        <v>2.75</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG43" t="n">
         <v>1.95</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>1.34</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="O44" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P44" t="n">
-        <v>4.26</v>
+        <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="R44" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="S44" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T44" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="U44" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="V44" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="W44" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X44" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AC44" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>1.34</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>2.62</v>
+        <v>1.16</v>
       </c>
       <c r="O45" t="n">
-        <v>2.78</v>
+        <v>6.25</v>
       </c>
       <c r="P45" t="n">
-        <v>2.77</v>
+        <v>9.75</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.74</v>
+        <v>1.55</v>
       </c>
       <c r="R45" t="n">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="S45" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="T45" t="n">
-        <v>2.11</v>
+        <v>4.75</v>
       </c>
       <c r="U45" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="V45" t="n">
-        <v>1.19</v>
+        <v>1.91</v>
       </c>
       <c r="W45" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="X45" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="Z45" t="n">
-        <v>2.55</v>
+        <v>7.5</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.63</v>
+        <v>1.31</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.43</v>
+        <v>2.92</v>
       </c>
       <c r="AC45" t="n">
-        <v>5.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF45" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.16</v>
+        <v>1.99</v>
       </c>
       <c r="O46" t="n">
-        <v>6.25</v>
+        <v>2.95</v>
       </c>
       <c r="P46" t="n">
-        <v>9.75</v>
+        <v>4.31</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.31</v>
+        <v>2.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.92</v>
+        <v>1.66</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -852,12 +852,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Qingdao Youth Island</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Chengdu Better City FC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.63</v>
+        <v>3.66</v>
       </c>
       <c r="R3" t="n">
-        <v>2.25</v>
+        <v>2.46</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="T3" t="n">
-        <v>2.65</v>
+        <v>3.28</v>
       </c>
       <c r="U3" t="n">
-        <v>2.63</v>
+        <v>2.34</v>
       </c>
       <c r="V3" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.85</v>
+        <v>2.21</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.1</v>
+        <v>1.16</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.64</v>
+        <v>1.11</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qingdao Youth Island</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chengdu Better City FC</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.66</v>
+        <v>4.72</v>
       </c>
       <c r="R4" t="n">
-        <v>2.46</v>
+        <v>2.03</v>
       </c>
       <c r="S4" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="T4" t="n">
-        <v>3.28</v>
+        <v>2.88</v>
       </c>
       <c r="U4" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="W4" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X4" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.21</v>
+        <v>1.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.83</v>
+        <v>2.03</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.72</v>
+        <v>2.63</v>
       </c>
       <c r="R5" t="n">
-        <v>2.03</v>
+        <v>2.25</v>
       </c>
       <c r="S5" t="n">
         <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.88</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
         <v>1.04</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y5" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="AA5" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.18</v>
+        <v>1.64</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>4.35</v>
+        <v>1.67</v>
       </c>
       <c r="O12" t="n">
         <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>1.71</v>
+        <v>4.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.1</v>
+        <v>2.32</v>
       </c>
       <c r="R12" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T12" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="V12" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.64</v>
+        <v>3.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.47</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.65</v>
+        <v>4.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.18</v>
+        <v>2.01</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,65 +2474,65 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.67</v>
+        <v>4.35</v>
       </c>
       <c r="O13" t="n">
         <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>4.95</v>
+        <v>1.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="S13" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T13" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U13" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.04</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.14</v>
+        <v>2.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="AB13" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.01</v>
+        <v>1.18</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2788,68 +2788,68 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5.24</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.57</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.28</v>
+        <v>5.24</v>
       </c>
       <c r="O17" t="n">
-        <v>5.4</v>
+        <v>3.57</v>
       </c>
       <c r="P17" t="n">
-        <v>6.75</v>
+        <v>1.48</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6</v>
+        <v>5.82</v>
       </c>
       <c r="R17" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="S17" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>3.82</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>2.75</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.21</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.06</v>
+        <v>1.26</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.26</v>
+        <v>1.92</v>
       </c>
       <c r="AB17" t="n">
-        <v>3.08</v>
+        <v>1.87</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.75</v>
+        <v>3.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.96</v>
+        <v>1.27</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.18</v>
+        <v>1.88</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.02</v>
+        <v>1.09</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="O19" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P19" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T19" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W19" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.33</v>
+        <v>4.52</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="AD19" t="n">
         <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="O20" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R20" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S20" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T20" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U20" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB20" t="n">
         <v>2.3</v>
       </c>
-      <c r="V20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC20" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="AD20" t="n">
         <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3873,12 +3873,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4022,22 +4022,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Estudiantes Caseros</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="AJ23" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4181,22 +4181,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Estudiantes Caseros</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -4223,64 +4223,64 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5304,12 +5304,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>São Bernardo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cuiabá</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5336,64 +5336,64 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="O31" t="n">
-        <v>2.63</v>
+        <v>3.24</v>
       </c>
       <c r="P31" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="R31" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S31" t="n">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>2.75</v>
       </c>
       <c r="U31" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="V31" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X31" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.63</v>
+        <v>1.33</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.12</v>
+        <v>3.01</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.83</v>
+        <v>2.16</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC31" t="n">
-        <v>5.75</v>
+        <v>3.75</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="AE31" t="n">
         <v>1.03</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.35</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5406,10 +5406,10 @@
         </is>
       </c>
       <c r="AJ31" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -5463,12 +5463,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>São Bernardo</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Cuiabá</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5495,64 +5495,64 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="O32" t="n">
-        <v>3.24</v>
+        <v>2.63</v>
       </c>
       <c r="P32" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="S32" t="n">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="T32" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="V32" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X32" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.01</v>
+        <v>2.12</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.16</v>
+        <v>2.83</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.75</v>
+        <v>5.75</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="AE32" t="n">
         <v>1.03</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5565,10 +5565,10 @@
         </is>
       </c>
       <c r="AJ32" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -6089,7 +6089,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6099,12 +6099,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -6131,64 +6131,64 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="O36" t="n">
-        <v>3.4</v>
+        <v>2.6</v>
       </c>
       <c r="P36" t="n">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>2.05</v>
+        <v>1.63</v>
       </c>
       <c r="S36" t="n">
-        <v>1.43</v>
+        <v>1.82</v>
       </c>
       <c r="T36" t="n">
-        <v>2.62</v>
+        <v>1.88</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="V36" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="W36" t="n">
         <v>1.02</v>
       </c>
       <c r="X36" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.29</v>
+        <v>1.77</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.09</v>
+        <v>3.6</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="AC36" t="n">
-        <v>3.68</v>
+        <v>6.55</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.85</v>
+        <v>2.55</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.85</v>
+        <v>1.42</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6201,10 +6201,10 @@
         </is>
       </c>
       <c r="AJ36" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="AK36" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -6290,64 +6290,64 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="P37" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.37</v>
+        <v>2.94</v>
       </c>
       <c r="R37" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S37" t="n">
         <v>1.32</v>
       </c>
       <c r="T37" t="n">
-        <v>2.92</v>
+        <v>3.11</v>
       </c>
       <c r="U37" t="n">
-        <v>2.47</v>
+        <v>2.51</v>
       </c>
       <c r="V37" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W37" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X37" t="n">
         <v>1.01</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AG37" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6360,10 +6360,10 @@
         </is>
       </c>
       <c r="AJ37" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.82</v>
+        <v>1.45</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6417,12 +6417,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6449,80 +6449,80 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="O38" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P38" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.56</v>
+        <v>2.37</v>
       </c>
       <c r="R38" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="S38" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="T38" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="U38" t="n">
-        <v>2.9</v>
+        <v>2.47</v>
       </c>
       <c r="V38" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="W38" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="X38" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.35</v>
+        <v>1.18</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.24</v>
+        <v>3.86</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.1</v>
+        <v>1.69</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AC38" t="n">
-        <v>3.9</v>
+        <v>2.62</v>
       </c>
       <c r="AD38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ38" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AK38" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6608,64 +6608,64 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="O39" t="n">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="P39" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>2.56</v>
       </c>
       <c r="R39" t="n">
-        <v>1.63</v>
+        <v>2.05</v>
       </c>
       <c r="S39" t="n">
-        <v>1.82</v>
+        <v>1.42</v>
       </c>
       <c r="T39" t="n">
-        <v>1.88</v>
+        <v>2.82</v>
       </c>
       <c r="U39" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="V39" t="n">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="W39" t="n">
         <v>1.02</v>
       </c>
       <c r="X39" t="n">
-        <v>1.16</v>
+        <v>1.04</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.77</v>
+        <v>1.35</v>
       </c>
       <c r="Z39" t="n">
-        <v>2</v>
+        <v>3.24</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="AC39" t="n">
-        <v>6.55</v>
+        <v>3.9</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.05</v>
+        <v>1.22</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF39" t="n">
-        <v>2.55</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6678,10 +6678,10 @@
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Supra du Québec</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6767,64 +6767,64 @@
         </is>
       </c>
       <c r="N40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O40" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P40" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Q40" t="n">
         <v>2.4</v>
       </c>
-      <c r="O40" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>2.94</v>
-      </c>
       <c r="R40" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S40" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="T40" t="n">
-        <v>3.11</v>
+        <v>2.62</v>
       </c>
       <c r="U40" t="n">
-        <v>2.51</v>
+        <v>3</v>
       </c>
       <c r="V40" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="W40" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X40" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z40" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AC40" t="n">
-        <v>2.74</v>
+        <v>3.68</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6837,10 +6837,10 @@
         </is>
       </c>
       <c r="AJ40" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.45</v>
+        <v>1.83</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -7043,7 +7043,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7053,12 +7053,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Delfin SC</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Macará</t>
+          <t>Guabirá</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -7085,64 +7085,64 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>2.62</v>
+        <v>1.16</v>
       </c>
       <c r="O42" t="n">
-        <v>2.78</v>
+        <v>6.25</v>
       </c>
       <c r="P42" t="n">
-        <v>2.77</v>
+        <v>9.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.74</v>
+        <v>1.55</v>
       </c>
       <c r="R42" t="n">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="S42" t="n">
-        <v>1.53</v>
+        <v>1.17</v>
       </c>
       <c r="T42" t="n">
-        <v>2.11</v>
+        <v>4.75</v>
       </c>
       <c r="U42" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="V42" t="n">
-        <v>1.19</v>
+        <v>1.91</v>
       </c>
       <c r="W42" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="X42" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="Z42" t="n">
-        <v>2.55</v>
+        <v>7.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>2.63</v>
+        <v>1.31</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.43</v>
+        <v>2.92</v>
       </c>
       <c r="AC42" t="n">
-        <v>5.3</v>
+        <v>1.85</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.14</v>
+        <v>1.85</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.03</v>
+        <v>1.33</v>
       </c>
       <c r="AF42" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.67</v>
+        <v>1.9</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7155,10 +7155,10 @@
         </is>
       </c>
       <c r="AJ42" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="AL42" t="n">
         <v>0</v>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7212,12 +7212,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7244,64 +7244,64 @@
         </is>
       </c>
       <c r="N43" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="O43" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="P43" t="n">
-        <v>4.26</v>
+        <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.4</v>
+        <v>3.01</v>
       </c>
       <c r="R43" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="S43" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="T43" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="U43" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="V43" t="n">
-        <v>1.42</v>
+        <v>1.29</v>
       </c>
       <c r="W43" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X43" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.21</v>
+        <v>1.44</v>
       </c>
       <c r="Z43" t="n">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.64</v>
+        <v>2.25</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="AC43" t="n">
-        <v>2.75</v>
+        <v>4.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>1.34</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL43" t="n">
         <v>0</v>
@@ -7371,12 +7371,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Fortaleza</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -7403,64 +7403,64 @@
         </is>
       </c>
       <c r="N44" t="n">
-        <v>2.25</v>
+        <v>1.99</v>
       </c>
       <c r="O44" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="P44" t="n">
-        <v>3</v>
+        <v>4.31</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AC44" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="AJ44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -7520,7 +7520,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guabirá</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7562,64 +7562,64 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>1.16</v>
+        <v>1.87</v>
       </c>
       <c r="O45" t="n">
-        <v>6.25</v>
+        <v>3.1</v>
       </c>
       <c r="P45" t="n">
-        <v>9.75</v>
+        <v>4.26</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="R45" t="n">
-        <v>3.2</v>
+        <v>2.23</v>
       </c>
       <c r="S45" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="T45" t="n">
-        <v>4.75</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
-        <v>1.8</v>
+        <v>2.6</v>
       </c>
       <c r="V45" t="n">
-        <v>1.91</v>
+        <v>1.42</v>
       </c>
       <c r="W45" t="n">
-        <v>1.22</v>
+        <v>1.05</v>
       </c>
       <c r="X45" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="Z45" t="n">
-        <v>7.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.31</v>
+        <v>1.64</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.92</v>
+        <v>1.69</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.85</v>
+        <v>2.75</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
         </is>
       </c>
       <c r="AJ45" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
       <c r="AK45" t="n">
-        <v>4.3</v>
+        <v>1.57</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7689,12 +7689,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>Delfin SC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Macará</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -7721,64 +7721,64 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1.99</v>
+        <v>2.62</v>
       </c>
       <c r="O46" t="n">
-        <v>2.95</v>
+        <v>2.78</v>
       </c>
       <c r="P46" t="n">
-        <v>4.31</v>
+        <v>2.77</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7791,10 +7791,10 @@
         </is>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>

--- a/jogos_2026-07-17.xlsx
+++ b/jogos_2026-07-17.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Changchun Yatai</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,65 +1043,65 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.83</v>
+        <v>1.95</v>
       </c>
       <c r="O4" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P4" t="n">
-        <v>1.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.72</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="S4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T4" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2.88</v>
       </c>
-      <c r="U4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA4" t="n">
+      <c r="AD4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AG4" t="n">
         <v>2</v>
       </c>
-      <c r="AB4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Changchun Yatai</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.03</v>
+        <v>3.17</v>
       </c>
       <c r="O5" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="P5" t="n">
-        <v>3.2</v>
+        <v>1.85</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.63</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S5" t="n">
         <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>2.96</v>
       </c>
       <c r="U5" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
         <v>1.05</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA5" t="n">
         <v>1.84</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
         <v>1.1</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AG5" t="n">
-        <v>2.07</v>
+        <v>1.84</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.64</v>
+        <v>1.18</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.21</v>
       </c>
       <c r="O6" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.56</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="S6" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="T6" t="n">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="U6" t="n">
-        <v>3.48</v>
+        <v>3.12</v>
       </c>
       <c r="V6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.04</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.49</v>
+        <v>2.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.41</v>
+        <v>2.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.65</v>
+        <v>3.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>1.03</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.58</v>
+        <v>2.97</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.48</v>
+        <v>4.56</v>
       </c>
       <c r="R7" t="n">
-        <v>2.07</v>
+        <v>1.82</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>2.28</v>
       </c>
       <c r="U7" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
         <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>AGMK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="O11" t="n">
-        <v>3.74</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>4.56</v>
+        <v>4.95</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="R11" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="S11" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="T11" t="n">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="U11" t="n">
-        <v>2.73</v>
+        <v>3.14</v>
       </c>
       <c r="V11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
         <v>1.37</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Z11" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.9</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Mash'al</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AGMK</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,65 +2315,65 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.67</v>
+        <v>4.35</v>
       </c>
       <c r="O12" t="n">
         <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>4.95</v>
+        <v>1.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.32</v>
+        <v>5.1</v>
       </c>
       <c r="R12" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="S12" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.44</v>
+        <v>2.31</v>
       </c>
       <c r="U12" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="V12" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.04</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.14</v>
+        <v>2.64</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.62</v>
       </c>
-      <c r="AC12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.01</v>
+        <v>1.18</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mash'al</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>4.35</v>
+        <v>1.64</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.74</v>
       </c>
       <c r="P13" t="n">
-        <v>1.71</v>
+        <v>4.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.1</v>
+        <v>2.16</v>
       </c>
       <c r="R13" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
-        <v>2.31</v>
+        <v>2.63</v>
       </c>
       <c r="U13" t="n">
-        <v>3.5</v>
+        <v>2.73</v>
       </c>
       <c r="V13" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X13" t="n">
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.64</v>
+        <v>3.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.47</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.51</v>
+        <v>1.9</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.65</v>
+        <v>3.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.11</v>
+        <v>1.88</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.18</v>
+        <v>2.15</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O14" t="n">
         <v>3.2</v>
@@ -2651,16 +2651,16 @@
         <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="V14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1.05</v>
@@ -2669,7 +2669,7 @@
         <v>1.35</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="AA14" t="n">
         <v>2.2</v>
@@ -2678,19 +2678,19 @@
         <v>1.64</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2788,68 +2788,68 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nõmme United</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2947,68 +2947,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3068,22 +3068,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Nõmme United</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>5.24</v>
+        <v>1.28</v>
       </c>
       <c r="O17" t="n">
-        <v>3.57</v>
+        <v>5.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.48</v>
+        <v>6.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.82</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.82</v>
       </c>
       <c r="U17" t="n">
-        <v>2.75</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="X17" t="n">
         <v>1.01</v>
       </c>
       <c r="Y17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.26</v>
       </c>
-      <c r="Z17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.87</v>
+        <v>3.08</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.14</v>
+        <v>1.75</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.27</v>
+        <v>1.96</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.09</v>
+        <v>3.02</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3237,12 +3237,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3269,64 +3269,64 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>5.64</v>
+        <v>4.5</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q18" t="n">
-        <v>5</v>
+        <v>5.82</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="T18" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="U18" t="n">
-        <v>2.34</v>
+        <v>2.75</v>
       </c>
       <c r="V18" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.71</v>
+        <v>3.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.55</v>
+        <v>1.93</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.24</v>
+        <v>1.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AG18" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="AJ18" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3396,12 +3396,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3428,64 +3428,64 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="O19" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="P19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R19" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T19" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="U19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AB19" t="n">
         <v>2.3</v>
       </c>
-      <c r="V19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AC19" t="n">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="AD19" t="n">
         <v>1.47</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3498,10 +3498,10 @@
         </is>
       </c>
       <c r="AJ19" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.97</v>
+        <v>1.88</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3555,12 +3555,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3587,64 +3587,64 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="O20" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="P20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T20" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="U20" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W20" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.33</v>
+        <v>4.52</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="AD20" t="n">
         <v>1.47</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="AJ20" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.88</v>
+        <v>1.97</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3905,64 +3905,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3975,10 +3975,10 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -4064,64 +4064,64 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.13</v>